--- a/2026/ROSALES/Marzo/expensas rosales Marzo.xlsx
+++ b/2026/ROSALES/Marzo/expensas rosales Marzo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ROSALES\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ROSALES\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D0DBE0-D6DA-4867-B038-D57CF9FB3C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57560F36-23B0-47DD-870A-5B436F4E06F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,16 +18,21 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$33</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="122">
   <si>
     <t>TOTAL</t>
   </si>
@@ -381,15 +386,6 @@
     <t>Espacio Edesur</t>
   </si>
   <si>
-    <t>Ascensores Lema - Puesta en marcha de ascensor - Trabajos realizados con mecanismos de puerta en 2do piso</t>
-  </si>
-  <si>
-    <t>No llego factura</t>
-  </si>
-  <si>
-    <t>ULTIMA CUOTA PLAN DE PAGOS 4B</t>
-  </si>
-  <si>
     <t>Vto. 17/04</t>
   </si>
   <si>
@@ -400,6 +396,9 @@
   </si>
   <si>
     <t>ARBA - Cuota 4 del plan</t>
+  </si>
+  <si>
+    <t>Fumigacion - Mes anterior</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1024,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1326,9 +1325,6 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1339,7 +1335,10 @@
     <xf numFmtId="43" fontId="26" fillId="6" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1351,12 +1350,6 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1378,10 +1371,10 @@
     <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1510,9 +1503,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1550,9 +1543,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1585,9 +1578,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1620,9 +1630,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1799,17 +1826,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1817,472 +1844,451 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="212" t="s">
         <v>102</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="215">
+      <c r="C18" s="199">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="28" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="212" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="214">
-        <v>358727.59</v>
+      <c r="C19" s="198">
+        <v>372886.04</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="28" t="s">
-        <v>10</v>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="212" t="s">
+        <v>25</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="214">
-        <v>372886.04</v>
+      <c r="C20" s="199">
+        <v>85000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="28" t="s">
-        <v>25</v>
+    <row r="21" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="212" t="s">
+        <v>120</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="215">
-        <v>85000</v>
+      <c r="C21" s="199">
+        <v>1034026.5</v>
       </c>
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="204" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="205"/>
-      <c r="C22" s="33">
-        <v>130000</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="215">
-        <v>1034026.5</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="28" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="212" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B22" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C22" s="199">
         <v>89200</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F22" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="40"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="23">
-        <f>SUM(C17:C24)</f>
-        <v>2146494.13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="35" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="40"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="23">
+        <f>SUM(C17:C22)</f>
+        <v>1657766.54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="178"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="178"/>
+      <c r="D24" s="45"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="199">
+        <f>384067+ (384067*3%)</f>
+        <v>395589.01</v>
+      </c>
+      <c r="D25" s="45"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="199">
+        <v>7458</v>
+      </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="33">
-        <f>349151.87+ (349151.87*10%)</f>
-        <v>384067.05699999997</v>
+        <v>0</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="215">
-        <v>7458</v>
+        <v>121</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="213">
+        <v>55000</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B29" s="42"/>
-      <c r="C29" s="33">
-        <v>84450</v>
-      </c>
-      <c r="D29" s="45"/>
+      <c r="C29" s="213">
+        <v>55000</v>
+      </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="192" t="s">
-        <v>118</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="6"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="6"/>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="23">
+        <f>SUM(C24:C30)</f>
+        <v>513047.01</v>
+      </c>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="23">
-        <f>SUM(C26:C31)</f>
-        <v>475975.05699999997</v>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="43">
+        <f>+C31+C23</f>
+        <v>2170813.5499999998</v>
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="43">
-        <f>+C32+C25</f>
-        <v>2622469.1869999999</v>
-      </c>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C33" s="24"/>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="24"/>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="173"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
       <c r="C36" s="173"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
-      <c r="C37" s="173"/>
+      <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="34"/>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C38" s="25"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C39" s="25"/>
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="157" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="157"/>
+      <c r="C39" s="158">
+        <v>0</v>
+      </c>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="157" t="s">
-        <v>113</v>
-      </c>
-      <c r="B40" s="157"/>
-      <c r="C40" s="158">
-        <v>500000</v>
-      </c>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C40" s="25"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C41" s="25"/>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="13" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="14">
-        <f>+C36+C37+C38+C41</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="6"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
+      <c r="B41" s="13"/>
+      <c r="C41" s="14">
+        <f>+C35+C36+C37+C40</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19">
-        <f>+C42+C33</f>
-        <v>2622469.1869999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-      <c r="C46" s="141"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="19">
+        <f>+C41+C32</f>
+        <v>2170813.5499999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="C45" s="141"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="163" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="164">
+        <v>1039280.7042474523</v>
+      </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="163" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B47" s="28"/>
-      <c r="C47" s="164">
-        <v>-141024.51037612878</v>
+      <c r="C47" s="177">
+        <f>-(C43-C30)</f>
+        <v>-2170813.5499999998</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="163" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="B48" s="28"/>
-      <c r="C48" s="177">
-        <f>-(C44-C31)</f>
-        <v>-2622469.1869999999</v>
-      </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C48" s="165">
+        <f>'prorrateo '!F31</f>
+        <v>3584406.0490640621</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="163" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B49" s="28"/>
-      <c r="C49" s="165">
-        <f>'prorrateo '!F31</f>
-        <v>4309983.1316235811</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C49" s="176">
+        <v>-1024355.45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="163" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B50" s="28"/>
-      <c r="C50" s="176">
-        <v>-1013211.13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C50" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="163" t="s">
-        <v>119</v>
+        <v>8</v>
       </c>
       <c r="B51" s="28"/>
-      <c r="C51" s="199">
-        <v>107386</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="163" t="s">
-        <v>109</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="163" t="s">
-        <v>8</v>
-      </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="164">
-        <f>SUM(C47:C52)</f>
-        <v>640664.3042474523</v>
-      </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="10"/>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="200"/>
-      <c r="B55" s="200"/>
-      <c r="C55" s="200"/>
-      <c r="F55" s="44"/>
-    </row>
-    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="201"/>
-      <c r="B56" s="201"/>
-      <c r="C56" s="201"/>
-    </row>
-    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="26" t="s">
+      <c r="C51" s="164">
+        <f>SUM(C46:C50)</f>
+        <v>1428517.7533115146</v>
+      </c>
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="9"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="10"/>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="200"/>
+      <c r="B53" s="200"/>
+      <c r="C53" s="200"/>
+      <c r="F53" s="44"/>
+    </row>
+    <row r="54" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="201"/>
+      <c r="B54" s="201"/>
+      <c r="C54" s="201"/>
+    </row>
+    <row r="55" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="29"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="28" t="s">
+      <c r="B55" s="27"/>
+      <c r="C55" s="29"/>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="28" t="s">
         <v>23</v>
       </c>
+      <c r="B56" s="28"/>
+      <c r="C56" s="31">
+        <f>-C41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="28"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="31"/>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="28"/>
       <c r="B58" s="28"/>
-      <c r="C58" s="31">
-        <f>-C42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="28"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="31"/>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="28"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="32"/>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="142" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="143"/>
-      <c r="C61" s="144">
-        <f>SUM(C57:C60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="202" t="s">
+      <c r="C58" s="32"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="142" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="143"/>
+      <c r="C59" s="144">
+        <f>SUM(C55:C58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="202" t="s">
         <v>105</v>
       </c>
+      <c r="B60" s="203"/>
+      <c r="C60" s="203"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="203"/>
+      <c r="B61" s="203"/>
+      <c r="C61" s="203"/>
+    </row>
+    <row r="62" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="203"/>
       <c r="B62" s="203"/>
       <c r="C62" s="203"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="203"/>
-      <c r="B63" s="203"/>
-      <c r="C63" s="203"/>
-    </row>
-    <row r="64" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="203"/>
-      <c r="B64" s="203"/>
-      <c r="C64" s="203"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A55:C56"/>
-    <mergeCell ref="A62:C64"/>
-    <mergeCell ref="A22:B22"/>
+  <mergeCells count="2">
+    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="A60:C62"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2301,58 +2307,58 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="11" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="206">
+      <c r="B1" s="204">
         <f>N1</f>
         <v>2249583.1469999999</v>
       </c>
-      <c r="C1" s="206"/>
+      <c r="C1" s="204"/>
       <c r="D1" s="135">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="207">
-        <v>0</v>
-      </c>
-      <c r="H1" s="207"/>
-      <c r="I1" s="208" t="s">
+      <c r="G1" s="205">
+        <v>0</v>
+      </c>
+      <c r="H1" s="205"/>
+      <c r="I1" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="J1" s="208"/>
-      <c r="K1" s="208"/>
-      <c r="L1" s="206">
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="204">
         <v>500000</v>
       </c>
-      <c r="M1" s="206"/>
+      <c r="M1" s="204"/>
       <c r="N1">
         <v>2249583.1469999999</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2396,7 +2402,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2410,11 +2416,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E3" s="126">
-        <v>245146.06472309006</v>
+        <v>196577.35914129001</v>
       </c>
       <c r="F3" s="175">
         <f t="shared" ref="F3" si="0">E3</f>
-        <v>245146.06472309006</v>
+        <v>196577.35914129001</v>
       </c>
       <c r="G3" s="181">
         <f>E3-F3</f>
@@ -2430,7 +2436,7 @@
       </c>
       <c r="J3" s="56">
         <f>Edesur!N10</f>
-        <v>57388.481725590005</v>
+        <v>70956.490479300017</v>
       </c>
       <c r="K3" s="56">
         <f>G$1*D3/100</f>
@@ -2442,15 +2448,15 @@
       </c>
       <c r="M3" s="57">
         <f>I3+G3+L3+K3+H3+J3</f>
-        <v>197892.18053729003</v>
+        <v>211460.18929100002</v>
       </c>
       <c r="N3" s="44"/>
       <c r="O3" s="138">
         <f>M3-J3</f>
-        <v>140503.69881170001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>140503.69881169999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2462,18 +2468,18 @@
         <v>5.09</v>
       </c>
       <c r="E4" s="126">
-        <v>237726.73859071001</v>
+        <v>305245.8364308484</v>
       </c>
       <c r="F4" s="175">
         <v>110474</v>
       </c>
       <c r="G4" s="181">
         <f t="shared" ref="G4:G29" si="1">E4-F4</f>
-        <v>127252.73859071001</v>
+        <v>194771.8364308484</v>
       </c>
       <c r="H4" s="56">
         <f t="shared" ref="H4:H29" si="2">IF(G4&gt;0,G4*4%,0)</f>
-        <v>5090.1095436284004</v>
+        <v>7790.8734572339363</v>
       </c>
       <c r="I4" s="56">
         <f t="shared" ref="I4:I29" si="3">B$1*D4/100</f>
@@ -2481,7 +2487,7 @@
       </c>
       <c r="J4" s="56">
         <f>Edesur!N11</f>
-        <v>34258.881438210017</v>
+        <v>61860.630546699955</v>
       </c>
       <c r="K4" s="56">
         <f t="shared" ref="K4:K29" si="4">G$1*D4/100</f>
@@ -2493,15 +2499,15 @@
       </c>
       <c r="M4" s="57">
         <f t="shared" ref="M4:M29" si="6">I4+G4+L4+K4+H4+J4</f>
-        <v>306555.51175484841</v>
+        <v>404377.12261708232</v>
       </c>
       <c r="N4" s="44"/>
       <c r="O4" s="138">
         <f t="shared" ref="O4:O29" si="7">M4-J4</f>
-        <v>272296.63031663839</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>342516.49207038234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2513,15 +2519,15 @@
         <v>5.04</v>
       </c>
       <c r="E5" s="126">
-        <v>254798.71871768872</v>
+        <v>204343.43875076872</v>
       </c>
       <c r="F5" s="175">
         <f>301940.37-F23</f>
-        <v>254798.71925147998</v>
+        <v>265339.25398188003</v>
       </c>
       <c r="G5" s="181">
         <f t="shared" si="1"/>
-        <v>-5.3379125893115997E-4</v>
+        <v>-60995.815231111308</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="2"/>
@@ -2533,7 +2539,7 @@
       </c>
       <c r="J5" s="56">
         <f>Edesur!N12</f>
-        <v>67061.258819759998</v>
+        <v>70267.6434152</v>
       </c>
       <c r="K5" s="56">
         <f t="shared" si="4"/>
@@ -2545,15 +2551,15 @@
       </c>
       <c r="M5" s="57">
         <f t="shared" si="6"/>
-        <v>205640.24889476874</v>
+        <v>147850.81879288869</v>
       </c>
       <c r="N5" s="44"/>
       <c r="O5" s="138">
         <f t="shared" si="7"/>
-        <v>138578.99007500874</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>77583.175377688691</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="62" t="s">
         <v>37</v>
       </c>
@@ -2565,11 +2571,11 @@
         <v>5.21</v>
       </c>
       <c r="E6" s="126">
-        <v>390207.9854617868</v>
+        <v>188205.46156518997</v>
       </c>
       <c r="F6" s="175">
         <f>E6</f>
-        <v>390207.9854617868</v>
+        <v>188205.46156518997</v>
       </c>
       <c r="G6" s="182">
         <f t="shared" si="1"/>
@@ -2585,7 +2591,7 @@
       </c>
       <c r="J6" s="64">
         <f>Edesur!N13</f>
-        <v>46292.731362489991</v>
+        <v>68548.147942300013</v>
       </c>
       <c r="K6" s="64">
         <f t="shared" si="4"/>
@@ -2597,7 +2603,7 @@
       </c>
       <c r="M6" s="174">
         <f t="shared" si="6"/>
-        <v>189546.01332118997</v>
+        <v>211801.429901</v>
       </c>
       <c r="O6" s="138">
         <f t="shared" si="7"/>
@@ -2605,7 +2611,7 @@
       </c>
       <c r="P6" s="159"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2619,15 +2625,15 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E7" s="126">
-        <v>244958.48660897004</v>
+        <v>199212.77119878004</v>
       </c>
       <c r="F7" s="175">
         <f>199250.14+92850-F28</f>
-        <v>244958.48925148</v>
+        <v>255499.02398188002</v>
       </c>
       <c r="G7" s="181">
         <f t="shared" si="1"/>
-        <v>-2.642509964061901E-3</v>
+        <v>-56286.252783099975</v>
       </c>
       <c r="H7" s="56">
         <f t="shared" si="2"/>
@@ -2639,7 +2645,7 @@
       </c>
       <c r="J7" s="56">
         <f>Edesur!N14</f>
-        <v>60023.896425589992</v>
+        <v>73516.875579300031</v>
       </c>
       <c r="K7" s="56">
         <f t="shared" si="4"/>
@@ -2651,15 +2657,15 @@
       </c>
       <c r="M7" s="57">
         <f t="shared" si="6"/>
-        <v>200527.59259478003</v>
+        <v>157734.32160790008</v>
       </c>
       <c r="O7" s="138">
         <f t="shared" si="7"/>
-        <v>140503.69616919005</v>
+        <v>84217.446028600054</v>
       </c>
       <c r="P7" s="159"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2671,11 +2677,11 @@
         <v>5.09</v>
       </c>
       <c r="E8" s="126">
-        <v>244451.26649070997</v>
+        <v>202248.94059650999</v>
       </c>
       <c r="F8" s="175">
         <f t="shared" ref="F8" si="8">E8</f>
-        <v>244451.26649070997</v>
+        <v>202248.94059650999</v>
       </c>
       <c r="G8" s="181">
         <f t="shared" si="1"/>
@@ -2691,7 +2697,7 @@
       </c>
       <c r="J8" s="56">
         <f>Edesur!N15</f>
-        <v>63604.833738209985</v>
+        <v>69204.152646699979</v>
       </c>
       <c r="K8" s="56">
         <f t="shared" si="4"/>
@@ -2703,14 +2709,14 @@
       </c>
       <c r="M8" s="57">
         <f t="shared" si="6"/>
-        <v>203558.61592050997</v>
+        <v>209157.93482899998</v>
       </c>
       <c r="O8" s="138">
         <f t="shared" si="7"/>
         <v>139953.7821823</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2722,11 +2728,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E9" s="126">
-        <v>231697.00892309</v>
+        <v>186016.94294129004</v>
       </c>
       <c r="F9" s="175">
         <f>E9</f>
-        <v>231697.00892309</v>
+        <v>186016.94294129004</v>
       </c>
       <c r="G9" s="181">
         <f t="shared" si="1"/>
@@ -2742,7 +2748,7 @@
       </c>
       <c r="J9" s="56">
         <f>Edesur!N16</f>
-        <v>46828.065525590013</v>
+        <v>69615.336379300003</v>
       </c>
       <c r="K9" s="56">
         <f t="shared" si="4"/>
@@ -2754,15 +2760,15 @@
       </c>
       <c r="M9" s="57">
         <f t="shared" si="6"/>
-        <v>187331.76433729002</v>
+        <v>210119.03519100003</v>
       </c>
       <c r="O9" s="138">
         <f t="shared" si="7"/>
-        <v>140503.69881170001</v>
+        <v>140503.69881170004</v>
       </c>
       <c r="P9" s="159"/>
     </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="190" t="s">
         <v>115</v>
       </c>
@@ -2774,7 +2780,7 @@
         <v>5.09</v>
       </c>
       <c r="E10" s="126">
-        <v>224924.81309071</v>
+        <v>176391.66853574003</v>
       </c>
       <c r="F10" s="175">
         <f>379452.66-107386-F22</f>
@@ -2782,7 +2788,7 @@
       </c>
       <c r="G10" s="182">
         <f t="shared" si="1"/>
-        <v>-0.19616076996317133</v>
+        <v>-48533.340715739934</v>
       </c>
       <c r="H10" s="64"/>
       <c r="I10" s="64">
@@ -2791,7 +2797,7 @@
       </c>
       <c r="J10" s="64">
         <f>Edesur!N17</f>
-        <v>37747.757838209996</v>
+        <v>63164.269846700008</v>
       </c>
       <c r="K10" s="64">
         <f t="shared" si="4"/>
@@ -2803,14 +2809,14 @@
       </c>
       <c r="M10" s="174">
         <f t="shared" si="6"/>
-        <v>177701.34385974004</v>
+        <v>154584.71131326008</v>
       </c>
       <c r="O10" s="138">
         <f t="shared" si="7"/>
-        <v>139953.58602153003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>91420.441466560063</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>94</v>
       </c>
@@ -2822,11 +2828,11 @@
         <v>5.04</v>
       </c>
       <c r="E11" s="126">
-        <v>379810.43677728315</v>
+        <v>182106.54158456001</v>
       </c>
       <c r="F11" s="175">
         <f>E11</f>
-        <v>379810.43677728315</v>
+        <v>182106.54158456001</v>
       </c>
       <c r="G11" s="181">
         <f t="shared" si="1"/>
@@ -2842,7 +2848,7 @@
       </c>
       <c r="J11" s="56">
         <f>Edesur!N18</f>
-        <v>44824.361119759997</v>
+        <v>66778.767015199977</v>
       </c>
       <c r="K11" s="56">
         <f t="shared" si="4"/>
@@ -2854,14 +2860,14 @@
       </c>
       <c r="M11" s="57">
         <f t="shared" si="6"/>
-        <v>183403.35172856</v>
+        <v>205357.75762399996</v>
       </c>
       <c r="O11" s="138">
         <f t="shared" si="7"/>
-        <v>138578.9906088</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>138578.99060879997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2873,11 +2879,11 @@
         <v>5.21</v>
       </c>
       <c r="E12" s="126">
-        <v>253412.57158498999</v>
+        <v>211989.84476518998</v>
       </c>
       <c r="F12" s="175">
         <f t="shared" ref="F12" si="9">E12</f>
-        <v>253412.57158498999</v>
+        <v>211989.84476518998</v>
       </c>
       <c r="G12" s="181">
         <f t="shared" si="1"/>
@@ -2893,7 +2899,7 @@
       </c>
       <c r="J12" s="56">
         <f>Edesur!N19</f>
-        <v>70077.114562489995</v>
+        <v>79933.889742300031</v>
       </c>
       <c r="K12" s="56">
         <f t="shared" si="4"/>
@@ -2905,14 +2911,14 @@
       </c>
       <c r="M12" s="57">
         <f t="shared" si="6"/>
-        <v>213330.39652118998</v>
+        <v>223187.17170100001</v>
       </c>
       <c r="O12" s="138">
         <f t="shared" si="7"/>
         <v>143253.28195869998</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2926,19 +2932,19 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E13" s="126">
-        <v>253624.40360897002</v>
+        <v>205111.98067307967</v>
       </c>
       <c r="F13" s="175">
         <f>300766.05-F24</f>
-        <v>253624.39925147998</v>
+        <v>264164.93398187996</v>
       </c>
       <c r="G13" s="181">
         <f t="shared" si="1"/>
-        <v>4.3574900482781231E-3</v>
+        <v>-59052.953308800294</v>
       </c>
       <c r="H13" s="56">
         <f t="shared" si="2"/>
-        <v>1.7429960193112492E-4</v>
+        <v>0</v>
       </c>
       <c r="I13" s="56">
         <f t="shared" si="3"/>
@@ -2946,7 +2952,7 @@
       </c>
       <c r="J13" s="56">
         <f>Edesur!N20</f>
-        <v>65923.098725590011</v>
+        <v>76808.799279299972</v>
       </c>
       <c r="K13" s="56">
         <f t="shared" si="4"/>
@@ -2958,15 +2964,15 @@
       </c>
       <c r="M13" s="57">
         <f t="shared" si="6"/>
-        <v>206426.80206907968</v>
+        <v>158259.54478219969</v>
       </c>
       <c r="N13" s="44"/>
       <c r="O13" s="138">
         <f t="shared" si="7"/>
-        <v>140503.70334348967</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>81450.745502899721</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
@@ -2980,19 +2986,19 @@
         <v>5.09</v>
       </c>
       <c r="E14" s="126">
-        <v>228413.77099358285</v>
+        <v>180752.96200829698</v>
       </c>
       <c r="F14" s="175">
         <f>275555.42-F25</f>
-        <v>228413.76925147997</v>
+        <v>238954.30398187999</v>
       </c>
       <c r="G14" s="182">
         <f t="shared" si="1"/>
-        <v>1.7421028751414269E-3</v>
+        <v>-58201.34197358301</v>
       </c>
       <c r="H14" s="64">
         <f t="shared" si="2"/>
-        <v>6.9684115005657076E-5</v>
+        <v>0</v>
       </c>
       <c r="I14" s="64">
         <f t="shared" si="3"/>
@@ -3000,7 +3006,7 @@
       </c>
       <c r="J14" s="56">
         <f>Edesur!N21</f>
-        <v>42108.853338209999</v>
+        <v>66728.175846700004</v>
       </c>
       <c r="K14" s="64">
         <f t="shared" si="4"/>
@@ -3012,14 +3018,14 @@
       </c>
       <c r="M14" s="57">
         <f t="shared" si="6"/>
-        <v>182062.63733229699</v>
+        <v>148480.61605541699</v>
       </c>
       <c r="O14" s="138">
         <f t="shared" si="7"/>
-        <v>139953.78399408699</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>81752.440208716987</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3033,16 +3039,16 @@
         <v>5.04</v>
       </c>
       <c r="E15" s="126">
-        <v>229298.04770269</v>
+        <v>441931.81109535758</v>
       </c>
       <c r="F15" s="175"/>
       <c r="G15" s="181">
         <f t="shared" si="1"/>
-        <v>229298.04770269</v>
+        <v>441931.81109535758</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="2"/>
-        <v>9171.9219081076008</v>
+        <v>17677.272443814305</v>
       </c>
       <c r="I15" s="56">
         <f t="shared" si="3"/>
@@ -3050,7 +3056,7 @@
       </c>
       <c r="J15" s="56">
         <f>Edesur!N22</f>
-        <v>66179.661019760024</v>
+        <v>-233958.62718480005</v>
       </c>
       <c r="K15" s="56">
         <f t="shared" si="4"/>
@@ -3062,14 +3068,14 @@
       </c>
       <c r="M15" s="57">
         <f t="shared" si="6"/>
-        <v>443228.62123935757</v>
+        <v>364229.44696317188</v>
       </c>
       <c r="O15" s="138">
         <f t="shared" si="7"/>
-        <v>377048.96021959756</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>598188.07414797193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3083,19 +3089,19 @@
         <v>5.21</v>
       </c>
       <c r="E16" s="126">
-        <v>257482.92123606999</v>
+        <v>200838.57252916362</v>
       </c>
       <c r="F16" s="175">
         <f>304624.57-F21</f>
-        <v>257482.91925147999</v>
+        <v>268023.45398187998</v>
       </c>
       <c r="G16" s="181">
         <f t="shared" si="1"/>
-        <v>1.9845899951178581E-3</v>
+        <v>-67184.881452716363</v>
       </c>
       <c r="H16" s="56">
         <f t="shared" si="2"/>
-        <v>7.9383599804714328E-5</v>
+        <v>0</v>
       </c>
       <c r="I16" s="56">
         <f t="shared" si="3"/>
@@ -3103,7 +3109,7 @@
       </c>
       <c r="J16" s="56">
         <f>Edesur!N23</f>
-        <v>58925.840262490019</v>
+        <v>76163.65234229996</v>
       </c>
       <c r="K16" s="56">
         <f t="shared" si="4"/>
@@ -3115,15 +3121,15 @@
       </c>
       <c r="M16" s="57">
         <f t="shared" si="6"/>
-        <v>202179.12428516359</v>
+        <v>152232.05284828358</v>
       </c>
       <c r="N16" s="44"/>
       <c r="O16" s="138">
         <f t="shared" si="7"/>
-        <v>143253.28402267356</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+        <v>76068.40050598362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3135,16 +3141,16 @@
         <v>5.04</v>
       </c>
       <c r="E17" s="126">
-        <v>97801.259959760006</v>
+        <v>276073.04574271035</v>
       </c>
       <c r="F17" s="175"/>
       <c r="G17" s="181">
         <f t="shared" si="1"/>
-        <v>97801.259959760006</v>
+        <v>276073.04574271035</v>
       </c>
       <c r="H17" s="56">
         <f t="shared" si="2"/>
-        <v>3912.0503983904005</v>
+        <v>11042.921829708413</v>
       </c>
       <c r="I17" s="56">
         <f t="shared" si="3"/>
@@ -3152,7 +3158,7 @@
       </c>
       <c r="J17" s="56">
         <f>Edesur!N24</f>
-        <v>37077.554919759983</v>
+        <v>61076.517415199996</v>
       </c>
       <c r="K17" s="56">
         <f t="shared" si="4"/>
@@ -3164,14 +3170,14 @@
       </c>
       <c r="M17" s="57">
         <f t="shared" si="6"/>
-        <v>277369.8558867104</v>
+        <v>486771.47559641872</v>
       </c>
       <c r="O17" s="138">
         <f t="shared" si="7"/>
-        <v>240292.30096695042</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>425694.95818121871</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="167" t="s">
         <v>61</v>
       </c>
@@ -3183,11 +3189,11 @@
         <v>5.21</v>
       </c>
       <c r="E18" s="126">
-        <v>239269.49198499002</v>
+        <v>191713.09536518998</v>
       </c>
       <c r="F18" s="175">
         <f t="shared" ref="F18:F21" si="10">E18</f>
-        <v>239269.49198499002</v>
+        <v>191713.09536518998</v>
       </c>
       <c r="G18" s="182">
         <f t="shared" si="1"/>
@@ -3203,7 +3209,7 @@
       </c>
       <c r="J18" s="56">
         <f>Edesur!N25</f>
-        <v>49800.365162490001</v>
+        <v>63136.638042300001</v>
       </c>
       <c r="K18" s="64">
         <f t="shared" si="4"/>
@@ -3215,7 +3221,7 @@
       </c>
       <c r="M18" s="57">
         <f t="shared" si="6"/>
-        <v>193053.64712118998</v>
+        <v>206389.92000099999</v>
       </c>
       <c r="N18" s="170"/>
       <c r="O18" s="138">
@@ -3225,7 +3231,7 @@
       <c r="P18" s="169"/>
       <c r="Q18" s="166"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
@@ -3237,11 +3243,11 @@
         <v>7.4</v>
       </c>
       <c r="E19" s="126">
-        <v>374177.79418060009</v>
+        <v>294818.42106860003</v>
       </c>
       <c r="F19" s="175">
         <f t="shared" si="10"/>
-        <v>374177.79418060009</v>
+        <v>294818.42106860003</v>
       </c>
       <c r="G19" s="182">
         <f t="shared" si="1"/>
@@ -3257,7 +3263,7 @@
       </c>
       <c r="J19" s="56">
         <f>Edesur!N26</f>
-        <v>93253.314830599993</v>
+        <v>89675.839061999985</v>
       </c>
       <c r="K19" s="64">
         <f t="shared" si="4"/>
@@ -3269,14 +3275,14 @@
       </c>
       <c r="M19" s="57">
         <f t="shared" si="6"/>
-        <v>296722.46770859999</v>
+        <v>293144.99193999998</v>
       </c>
       <c r="O19" s="138">
         <f t="shared" si="7"/>
         <v>203469.15287799999</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="62" t="s">
         <v>116</v>
       </c>
@@ -3288,14 +3294,14 @@
         <v>1.08</v>
       </c>
       <c r="E20" s="126">
-        <v>399381.20189270412</v>
+        <v>435982.31791082409</v>
       </c>
       <c r="F20" s="175">
         <v>0</v>
       </c>
       <c r="G20" s="182">
         <f t="shared" si="1"/>
-        <v>399381.20189270412</v>
+        <v>435982.31791082409</v>
       </c>
       <c r="H20" s="64"/>
       <c r="I20" s="64">
@@ -3304,7 +3310,7 @@
       </c>
       <c r="J20" s="64">
         <f>Edesur!N27</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K20" s="64">
         <f t="shared" si="4"/>
@@ -3316,14 +3322,14 @@
       </c>
       <c r="M20" s="174">
         <f t="shared" si="6"/>
-        <v>436260.20579882408</v>
+        <v>478765.64105882408</v>
       </c>
       <c r="O20" s="138">
         <f t="shared" si="7"/>
-        <v>429076.69988030411</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+        <v>465677.81589842407</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3335,11 +3341,11 @@
         <v>1.08</v>
       </c>
       <c r="E21" s="126">
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="F21" s="175">
         <f t="shared" si="10"/>
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="G21" s="181">
         <f t="shared" si="1"/>
@@ -3355,7 +3361,7 @@
       </c>
       <c r="J21" s="56">
         <f>Edesur!N28</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K21" s="56">
         <f t="shared" si="4"/>
@@ -3367,14 +3373,14 @@
       </c>
       <c r="M21" s="57">
         <f t="shared" si="6"/>
-        <v>36879.00390612</v>
+        <v>42783.323148000003</v>
       </c>
       <c r="O21" s="138">
         <f t="shared" si="7"/>
         <v>29695.4979876</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="62" t="s">
         <v>115</v>
       </c>
@@ -3386,14 +3392,14 @@
         <v>1.08</v>
       </c>
       <c r="E22" s="126">
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="F22" s="175">
         <v>47141.650748520005</v>
       </c>
       <c r="G22" s="182">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-10540.53473040001</v>
       </c>
       <c r="H22" s="64">
         <f t="shared" si="2"/>
@@ -3405,7 +3411,7 @@
       </c>
       <c r="J22" s="64">
         <f>Edesur!N29</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K22" s="64">
         <f t="shared" si="4"/>
@@ -3417,14 +3423,14 @@
       </c>
       <c r="M22" s="174">
         <f t="shared" si="6"/>
-        <v>36879.00390612</v>
+        <v>32242.788417599993</v>
       </c>
       <c r="O22" s="138">
         <f t="shared" si="7"/>
-        <v>29695.4979876</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+        <v>19154.96325719999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3436,11 +3442,11 @@
         <v>1.08</v>
       </c>
       <c r="E23" s="126">
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="F23" s="175">
         <f>E23</f>
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="G23" s="181">
         <f t="shared" si="1"/>
@@ -3456,7 +3462,7 @@
       </c>
       <c r="J23" s="56">
         <f>Edesur!N30</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K23" s="56">
         <f t="shared" si="4"/>
@@ -3468,14 +3474,14 @@
       </c>
       <c r="M23" s="57">
         <f t="shared" si="6"/>
-        <v>36879.00390612</v>
+        <v>42783.323148000003</v>
       </c>
       <c r="O23" s="138">
         <f t="shared" si="7"/>
         <v>29695.4979876</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3489,11 +3495,11 @@
         <v>1.08</v>
       </c>
       <c r="E24" s="126">
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="F24" s="175">
         <f t="shared" ref="F24" si="11">E24</f>
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="G24" s="181">
         <f t="shared" si="1"/>
@@ -3509,7 +3515,7 @@
       </c>
       <c r="J24" s="56">
         <f>Edesur!N31</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K24" s="56">
         <f t="shared" si="4"/>
@@ -3521,14 +3527,14 @@
       </c>
       <c r="M24" s="57">
         <f t="shared" si="6"/>
-        <v>36879.00390612</v>
+        <v>42783.323148000003</v>
       </c>
       <c r="O24" s="138">
         <f t="shared" si="7"/>
         <v>29695.4979876</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -3542,11 +3548,11 @@
         <v>1.08</v>
       </c>
       <c r="E25" s="126">
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="F25" s="175">
         <f>E25</f>
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="G25" s="181">
         <f t="shared" si="1"/>
@@ -3562,7 +3568,7 @@
       </c>
       <c r="J25" s="56">
         <f>Edesur!N32</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K25" s="56">
         <f t="shared" si="4"/>
@@ -3574,14 +3580,14 @@
       </c>
       <c r="M25" s="57">
         <f t="shared" si="6"/>
-        <v>36879.00390612</v>
+        <v>42783.323148000003</v>
       </c>
       <c r="O25" s="138">
         <f t="shared" si="7"/>
         <v>29695.4979876</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3593,11 +3599,11 @@
         <v>1.08</v>
       </c>
       <c r="E26" s="126">
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="F26" s="175">
         <f t="shared" ref="F26:F28" si="12">E26</f>
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="G26" s="181">
         <f t="shared" si="1"/>
@@ -3613,7 +3619,7 @@
       </c>
       <c r="J26" s="56">
         <f>Edesur!N33</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K26" s="56">
         <f t="shared" si="4"/>
@@ -3625,14 +3631,14 @@
       </c>
       <c r="M26" s="57">
         <f t="shared" si="6"/>
-        <v>36879.00390612</v>
+        <v>42783.323148000003</v>
       </c>
       <c r="O26" s="138">
         <f t="shared" si="7"/>
         <v>29695.4979876</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3644,11 +3650,11 @@
         <v>1.08</v>
       </c>
       <c r="E27" s="126">
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="F27" s="175">
         <f t="shared" si="12"/>
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="G27" s="181">
         <f t="shared" si="1"/>
@@ -3664,7 +3670,7 @@
       </c>
       <c r="J27" s="56">
         <f>Edesur!N34</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K27" s="56">
         <f t="shared" si="4"/>
@@ -3676,7 +3682,7 @@
       </c>
       <c r="M27" s="57">
         <f t="shared" si="6"/>
-        <v>36879.00390612</v>
+        <v>42783.323148000003</v>
       </c>
       <c r="O27" s="138">
         <f t="shared" si="7"/>
@@ -3684,10 +3690,10 @@
       </c>
       <c r="P27" s="44">
         <f>F27+F26+F19</f>
-        <v>468461.09567764011</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+        <v>368020.65310484002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3700,11 +3706,11 @@
         <v>1.08</v>
       </c>
       <c r="E28" s="126">
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="F28" s="175">
         <f t="shared" si="12"/>
-        <v>47141.650748520005</v>
+        <v>36601.116018119996</v>
       </c>
       <c r="G28" s="181">
         <f t="shared" si="1"/>
@@ -3720,7 +3726,7 @@
       </c>
       <c r="J28" s="56">
         <f>Edesur!N35</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" si="4"/>
@@ -3732,14 +3738,14 @@
       </c>
       <c r="M28" s="57">
         <f t="shared" si="6"/>
-        <v>36879.00390612</v>
+        <v>42783.323148000003</v>
       </c>
       <c r="O28" s="138">
         <f t="shared" si="7"/>
         <v>29695.4979876</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3753,16 +3759,16 @@
         <v>1.08</v>
       </c>
       <c r="E29" s="126">
-        <v>47141.650748520005</v>
+        <v>85628.43279658079</v>
       </c>
       <c r="F29" s="175"/>
       <c r="G29" s="181">
         <f t="shared" si="1"/>
-        <v>47141.650748520005</v>
+        <v>85628.43279658079</v>
       </c>
       <c r="H29" s="56">
         <f t="shared" si="2"/>
-        <v>1885.6660299408002</v>
+        <v>3425.1373118632318</v>
       </c>
       <c r="I29" s="56">
         <f t="shared" si="3"/>
@@ -3770,7 +3776,7 @@
       </c>
       <c r="J29" s="56">
         <f>Edesur!N36</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="K29" s="56">
         <f t="shared" si="4"/>
@@ -3782,14 +3788,14 @@
       </c>
       <c r="M29" s="57">
         <f t="shared" si="6"/>
-        <v>85906.320684580787</v>
+        <v>131836.89325644402</v>
       </c>
       <c r="O29" s="138">
         <f t="shared" si="7"/>
-        <v>78722.814766060794</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+        <v>118749.06809604402</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3804,7 +3810,7 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3817,7 +3823,7 @@
       <c r="E31" s="73"/>
       <c r="F31" s="132">
         <f>SUM(F3:F30)</f>
-        <v>4309983.1316235811</v>
+        <v>3584406.0490640621</v>
       </c>
       <c r="G31" s="75"/>
       <c r="H31" s="75"/>
@@ -3833,16 +3839,16 @@
       <c r="L31" s="132"/>
       <c r="M31" s="132">
         <f>SUM(M3:M29)</f>
-        <v>4683728.7328449283</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>4887467.1258234903</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K32" s="22"/>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F34" s="44"/>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E36" s="21"/>
     </row>
   </sheetData>
@@ -3861,45 +3867,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="0.109375" customWidth="1"/>
-    <col min="6" max="6" width="12" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="5.109375" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="209" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="207" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="210"/>
-      <c r="C1" s="210"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="211"/>
+      <c r="B1" s="208"/>
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
+      <c r="K1" s="208"/>
+      <c r="L1" s="208"/>
+      <c r="M1" s="208"/>
+      <c r="N1" s="209"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="146"/>
@@ -3917,7 +3923,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="148"/>
@@ -3935,7 +3941,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="148"/>
@@ -3955,7 +3961,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="148"/>
@@ -3973,7 +3979,7 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
       <c r="C6" s="172" t="str">
@@ -3994,14 +4000,14 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
       <c r="C7" s="180">
-        <f>-'detalle y gastos'!C50</f>
-        <v>1013211.13</v>
+        <f>-'detalle y gastos'!C49</f>
+        <v>1024355.45</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="146"/>
@@ -4017,7 +4023,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -4031,18 +4037,18 @@
       <c r="J8" s="78"/>
       <c r="K8" s="179">
         <f>C8-J38</f>
-        <v>-348071.69310000003</v>
-      </c>
-      <c r="L8" s="213">
+        <v>187480.21300000005</v>
+      </c>
+      <c r="L8" s="211">
         <f>C7-J38</f>
-        <v>665139.43689999997</v>
-      </c>
-      <c r="M8" s="213"/>
+        <v>1211835.6629999999</v>
+      </c>
+      <c r="M8" s="211"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="86" t="s">
         <v>78</v>
       </c>
@@ -4087,7 +4093,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="97">
         <v>1</v>
       </c>
@@ -4104,46 +4110,46 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F10" s="102">
-        <v>4893.5</v>
+        <v>5143</v>
       </c>
       <c r="G10" s="102">
-        <v>5143</v>
+        <v>5239.3</v>
       </c>
       <c r="H10" s="103">
         <f>G10-F10</f>
-        <v>249.5</v>
+        <v>96.300000000000182</v>
       </c>
       <c r="I10" s="104">
         <f t="shared" ref="I10:I37" si="0">H10*7%</f>
-        <v>17.465000000000003</v>
+        <v>6.741000000000013</v>
       </c>
       <c r="J10" s="114">
         <f>M10*93.787</f>
-        <v>23399.856500000002</v>
+        <v>9031.6881000000176</v>
       </c>
       <c r="K10" s="114">
         <f>K8*E10%</f>
-        <v>-17786.463517410004</v>
+        <v>9580.2388843000044</v>
       </c>
       <c r="L10" s="186">
         <f>L$8*E10/S$12</f>
-        <v>33988.625225590004</v>
+        <v>61924.802379299996</v>
       </c>
       <c r="M10" s="105">
         <f>G10-F10</f>
-        <v>249.5</v>
+        <v>96.300000000000182</v>
       </c>
       <c r="N10" s="103">
         <f>J10+L10</f>
-        <v>57388.481725590005</v>
+        <v>70956.490479300017</v>
       </c>
       <c r="O10" s="96">
         <f>N10+'prorrateo '!M3</f>
-        <v>255280.66226288004</v>
+        <v>282416.67977030005</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="98">
         <v>2</v>
       </c>
@@ -4160,46 +4166,46 @@
         <v>5.09</v>
       </c>
       <c r="F11" s="102">
-        <v>4543.8</v>
+        <v>4548.1000000000004</v>
       </c>
       <c r="G11" s="102">
-        <v>4548.1000000000004</v>
+        <v>4550</v>
       </c>
       <c r="H11" s="103">
         <f t="shared" ref="H11:H27" si="1">G11-F11</f>
-        <v>4.3000000000001819</v>
+        <v>1.8999999999996362</v>
       </c>
       <c r="I11" s="104">
         <f t="shared" si="0"/>
-        <v>0.30100000000001276</v>
+        <v>0.13299999999997456</v>
       </c>
       <c r="J11" s="114">
         <f t="shared" ref="J11:J26" si="2">M11*93.787</f>
-        <v>403.28410000001708</v>
+        <v>178.1952999999659</v>
       </c>
       <c r="K11" s="114">
         <f>K8*E11%</f>
-        <v>-17716.849178790002</v>
+        <v>9542.7428417000028</v>
       </c>
       <c r="L11" s="186">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>33855.597338209998</v>
+        <v>61682.435246699992</v>
       </c>
       <c r="M11" s="105">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
-        <v>4.3000000000001819</v>
+        <v>1.8999999999996362</v>
       </c>
       <c r="N11" s="103">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>34258.881438210017</v>
+        <v>61860.630546699955</v>
       </c>
       <c r="O11" s="96">
         <f>N11+'prorrateo '!M4</f>
-        <v>340814.39319305844</v>
+        <v>466237.7531637823</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="97">
         <v>3</v>
       </c>
@@ -4216,49 +4222,49 @@
         <v>5.04</v>
       </c>
       <c r="F12" s="102">
-        <v>2352.9</v>
+        <v>2710.5</v>
       </c>
       <c r="G12" s="102">
-        <v>2710.5</v>
+        <v>2808.5</v>
       </c>
       <c r="H12" s="103">
         <f t="shared" si="1"/>
-        <v>357.59999999999991</v>
+        <v>98</v>
       </c>
       <c r="I12" s="104">
         <f t="shared" si="0"/>
-        <v>25.031999999999996</v>
+        <v>6.86</v>
       </c>
       <c r="J12" s="114">
         <f t="shared" si="2"/>
-        <v>33538.231199999995</v>
+        <v>9191.1260000000002</v>
       </c>
       <c r="K12" s="114">
         <f>K8*E12%</f>
-        <v>-17542.813332240003</v>
+        <v>9449.0027352000016</v>
       </c>
       <c r="L12" s="186">
         <f t="shared" si="3"/>
-        <v>33523.027619759996</v>
+        <v>61076.517415199996</v>
       </c>
       <c r="M12" s="105">
         <f>G12-F12</f>
-        <v>357.59999999999991</v>
+        <v>98</v>
       </c>
       <c r="N12" s="103">
         <f t="shared" si="5"/>
-        <v>67061.258819759998</v>
+        <v>70267.6434152</v>
       </c>
       <c r="O12" s="96">
         <f>N12+'prorrateo '!M5</f>
-        <v>272701.50771452871</v>
+        <v>218118.46220808869</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="97">
         <v>4</v>
       </c>
@@ -4275,46 +4281,46 @@
         <v>5.21</v>
       </c>
       <c r="F13" s="102">
-        <v>1511.5</v>
+        <v>1635.6</v>
       </c>
       <c r="G13" s="102">
-        <v>1635.6</v>
+        <v>1693.3</v>
       </c>
       <c r="H13" s="103">
         <f t="shared" si="1"/>
-        <v>124.09999999999991</v>
+        <v>57.700000000000045</v>
       </c>
       <c r="I13" s="151">
         <f t="shared" si="0"/>
-        <v>8.6869999999999941</v>
+        <v>4.0390000000000033</v>
       </c>
       <c r="J13" s="114">
         <f t="shared" si="2"/>
-        <v>11638.966699999992</v>
+        <v>5411.5099000000046</v>
       </c>
       <c r="K13" s="187">
         <f>K8*E13%</f>
-        <v>-18134.535210510003</v>
+        <v>9767.7190973000033</v>
       </c>
       <c r="L13" s="186">
         <f t="shared" si="3"/>
-        <v>34653.764662490001</v>
+        <v>63136.638042300001</v>
       </c>
       <c r="M13" s="152">
         <f t="shared" si="4"/>
-        <v>124.09999999999991</v>
+        <v>57.700000000000045</v>
       </c>
       <c r="N13" s="103">
         <f t="shared" si="5"/>
-        <v>46292.731362489991</v>
+        <v>68548.147942300013</v>
       </c>
       <c r="O13" s="96">
         <f>N13+'prorrateo '!M6</f>
-        <v>235838.74468367995</v>
+        <v>280349.57784330001</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="97">
         <v>6</v>
       </c>
@@ -4331,46 +4337,46 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F14" s="102">
-        <v>2363.6</v>
+        <v>2641.2</v>
       </c>
       <c r="G14" s="102">
-        <v>2641.2</v>
+        <v>2764.8</v>
       </c>
       <c r="H14" s="103">
         <f t="shared" si="1"/>
-        <v>277.59999999999991</v>
+        <v>123.60000000000036</v>
       </c>
       <c r="I14" s="104">
         <f t="shared" si="0"/>
-        <v>19.431999999999995</v>
+        <v>8.6520000000000259</v>
       </c>
       <c r="J14" s="114">
         <f t="shared" si="2"/>
-        <v>26035.271199999992</v>
+        <v>11592.073200000035</v>
       </c>
       <c r="K14" s="114">
         <f>K8*E14%</f>
-        <v>-17786.463517410004</v>
+        <v>9580.2388843000044</v>
       </c>
       <c r="L14" s="186">
         <f t="shared" si="3"/>
-        <v>33988.625225590004</v>
+        <v>61924.802379299996</v>
       </c>
       <c r="M14" s="105">
         <f t="shared" si="4"/>
-        <v>277.59999999999991</v>
+        <v>123.60000000000036</v>
       </c>
       <c r="N14" s="103">
         <f t="shared" si="5"/>
-        <v>60023.896425589992</v>
+        <v>73516.875579300031</v>
       </c>
       <c r="O14" s="96">
         <f>N14+'prorrateo '!M7</f>
-        <v>260551.48902037001</v>
+        <v>231251.19718720013</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="97">
         <v>7</v>
       </c>
@@ -4387,45 +4393,45 @@
         <v>5.09</v>
       </c>
       <c r="F15" s="102">
-        <v>3564.3</v>
+        <v>3881.5</v>
       </c>
       <c r="G15" s="102">
-        <v>3881.5</v>
+        <v>3961.7</v>
       </c>
       <c r="H15" s="103">
         <f t="shared" si="1"/>
-        <v>317.19999999999982</v>
+        <v>80.199999999999818</v>
       </c>
       <c r="I15" s="104">
         <f t="shared" si="0"/>
-        <v>22.20399999999999</v>
+        <v>5.6139999999999874</v>
       </c>
       <c r="J15" s="114">
         <f t="shared" si="2"/>
-        <v>29749.236399999983</v>
+        <v>7521.7173999999832</v>
       </c>
       <c r="K15" s="114">
         <f>K8*E15%</f>
-        <v>-17716.849178790002</v>
+        <v>9542.7428417000028</v>
       </c>
       <c r="L15" s="186">
         <f t="shared" si="3"/>
-        <v>33855.597338209998</v>
+        <v>61682.435246699992</v>
       </c>
       <c r="M15" s="105">
         <f t="shared" si="4"/>
-        <v>317.19999999999982</v>
+        <v>80.199999999999818</v>
       </c>
       <c r="N15" s="103">
         <f t="shared" si="5"/>
-        <v>63604.833738209985</v>
+        <v>69204.152646699979</v>
       </c>
       <c r="O15" s="96">
         <f>N15+'prorrateo '!M8</f>
-        <v>267163.44965871994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>278362.08747569995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="97">
         <v>8</v>
       </c>
@@ -4442,45 +4448,45 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F16" s="102">
-        <v>2836.7</v>
+        <v>2973.6</v>
       </c>
       <c r="G16" s="102">
-        <v>2973.6</v>
+        <v>3055.6</v>
       </c>
       <c r="H16" s="103">
         <f t="shared" si="1"/>
-        <v>136.90000000000009</v>
+        <v>82</v>
       </c>
       <c r="I16" s="104">
         <f t="shared" si="0"/>
-        <v>9.5830000000000073</v>
+        <v>5.74</v>
       </c>
       <c r="J16" s="114">
         <f t="shared" si="2"/>
-        <v>12839.440300000009</v>
+        <v>7690.5340000000006</v>
       </c>
       <c r="K16" s="114">
         <f>K8*E16%</f>
-        <v>-17786.463517410004</v>
+        <v>9580.2388843000044</v>
       </c>
       <c r="L16" s="186">
         <f t="shared" si="3"/>
-        <v>33988.625225590004</v>
+        <v>61924.802379299996</v>
       </c>
       <c r="M16" s="105">
         <f t="shared" si="4"/>
-        <v>136.90000000000009</v>
+        <v>82</v>
       </c>
       <c r="N16" s="103">
         <f t="shared" si="5"/>
-        <v>46828.065525590013</v>
+        <v>69615.336379300003</v>
       </c>
       <c r="O16" s="96">
         <f>N16+'prorrateo '!M9</f>
-        <v>234159.82986288003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>279734.37157030002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="97">
         <v>9</v>
       </c>
@@ -4497,45 +4503,45 @@
         <v>5.09</v>
       </c>
       <c r="F17" s="102">
-        <v>3459.5</v>
+        <v>3501</v>
       </c>
       <c r="G17" s="102">
-        <v>3501</v>
+        <v>3516.8</v>
       </c>
       <c r="H17" s="103">
         <f t="shared" si="1"/>
-        <v>41.5</v>
+        <v>15.800000000000182</v>
       </c>
       <c r="I17" s="104">
         <f t="shared" si="0"/>
-        <v>2.9050000000000002</v>
+        <v>1.1060000000000128</v>
       </c>
       <c r="J17" s="114">
         <f t="shared" si="2"/>
-        <v>3892.1605000000004</v>
+        <v>1481.8346000000172</v>
       </c>
       <c r="K17" s="114">
         <f>K8*E17%</f>
-        <v>-17716.849178790002</v>
+        <v>9542.7428417000028</v>
       </c>
       <c r="L17" s="186">
         <f t="shared" si="3"/>
-        <v>33855.597338209998</v>
+        <v>61682.435246699992</v>
       </c>
       <c r="M17" s="105">
         <f t="shared" si="4"/>
-        <v>41.5</v>
+        <v>15.800000000000182</v>
       </c>
       <c r="N17" s="103">
         <f t="shared" si="5"/>
-        <v>37747.757838209996</v>
+        <v>63164.269846700008</v>
       </c>
       <c r="O17" s="96">
         <f>N17+'prorrateo '!M10</f>
-        <v>215449.10169795004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>217748.98115996009</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="97">
         <v>10</v>
       </c>
@@ -4552,45 +4558,45 @@
         <v>5.04</v>
       </c>
       <c r="F18" s="102">
-        <v>2601.9</v>
+        <v>2722.4</v>
       </c>
       <c r="G18" s="102">
-        <v>2722.4</v>
+        <v>2783.2</v>
       </c>
       <c r="H18" s="103">
         <f t="shared" si="1"/>
-        <v>120.5</v>
+        <v>60.799999999999727</v>
       </c>
       <c r="I18" s="104">
         <f t="shared" si="0"/>
-        <v>8.4350000000000005</v>
+        <v>4.2559999999999816</v>
       </c>
       <c r="J18" s="114">
         <f t="shared" si="2"/>
-        <v>11301.333500000001</v>
+        <v>5702.2495999999746</v>
       </c>
       <c r="K18" s="114">
         <f>K8*E18%</f>
-        <v>-17542.813332240003</v>
+        <v>9449.0027352000016</v>
       </c>
       <c r="L18" s="186">
         <f t="shared" si="3"/>
-        <v>33523.027619759996</v>
+        <v>61076.517415199996</v>
       </c>
       <c r="M18" s="105">
         <f t="shared" si="4"/>
-        <v>120.5</v>
+        <v>60.799999999999727</v>
       </c>
       <c r="N18" s="103">
         <f t="shared" si="5"/>
-        <v>44824.361119759997</v>
+        <v>66778.767015199977</v>
       </c>
       <c r="O18" s="96">
         <f>N18+'prorrateo '!M11</f>
-        <v>228227.71284831999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>272136.52463919995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="97">
         <v>11</v>
       </c>
@@ -4607,45 +4613,45 @@
         <v>5.21</v>
       </c>
       <c r="F19" s="102">
-        <v>5191</v>
+        <v>5568.7</v>
       </c>
       <c r="G19" s="102">
-        <v>5568.7</v>
+        <v>5747.8</v>
       </c>
       <c r="H19" s="103">
         <f t="shared" si="1"/>
-        <v>377.69999999999982</v>
+        <v>179.10000000000036</v>
       </c>
       <c r="I19" s="104">
         <f t="shared" si="0"/>
-        <v>26.438999999999989</v>
+        <v>12.537000000000027</v>
       </c>
       <c r="J19" s="114">
         <f t="shared" si="2"/>
-        <v>35423.349899999987</v>
+        <v>16797.251700000033</v>
       </c>
       <c r="K19" s="114">
         <f>K8*E19%</f>
-        <v>-18134.535210510003</v>
+        <v>9767.7190973000033</v>
       </c>
       <c r="L19" s="186">
         <f t="shared" si="3"/>
-        <v>34653.764662490001</v>
+        <v>63136.638042300001</v>
       </c>
       <c r="M19" s="105">
         <f>G19-F19</f>
-        <v>377.69999999999982</v>
+        <v>179.10000000000036</v>
       </c>
       <c r="N19" s="103">
         <f t="shared" si="5"/>
-        <v>70077.114562489995</v>
+        <v>79933.889742300031</v>
       </c>
       <c r="O19" s="96">
         <f>N19+'prorrateo '!M12</f>
-        <v>283407.51108367997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>303121.06144330004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="97">
         <v>12</v>
       </c>
@@ -4662,45 +4668,45 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F20" s="102">
-        <v>6705</v>
+        <v>7045.5</v>
       </c>
       <c r="G20" s="102">
-        <v>7045.5</v>
+        <v>7204.2</v>
       </c>
       <c r="H20" s="103">
         <f t="shared" si="1"/>
-        <v>340.5</v>
+        <v>158.69999999999982</v>
       </c>
       <c r="I20" s="104">
         <f t="shared" si="0"/>
-        <v>23.835000000000001</v>
+        <v>11.108999999999988</v>
       </c>
       <c r="J20" s="114">
         <f t="shared" si="2"/>
-        <v>31934.473500000004</v>
+        <v>14883.996899999984</v>
       </c>
       <c r="K20" s="114">
         <f>K8*E20%</f>
-        <v>-17786.463517410004</v>
+        <v>9580.2388843000044</v>
       </c>
       <c r="L20" s="186">
         <f t="shared" si="3"/>
-        <v>33988.625225590004</v>
+        <v>61924.802379299996</v>
       </c>
       <c r="M20" s="105">
         <f t="shared" si="4"/>
-        <v>340.5</v>
+        <v>158.69999999999982</v>
       </c>
       <c r="N20" s="103">
         <f t="shared" si="5"/>
-        <v>65923.098725590011</v>
+        <v>76808.799279299972</v>
       </c>
       <c r="O20" s="96">
         <f>N20+'prorrateo '!M13</f>
-        <v>272349.90079466969</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>235068.34406149967</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="97">
         <v>13</v>
       </c>
@@ -4717,45 +4723,45 @@
         <v>5.09</v>
       </c>
       <c r="F21" s="102">
-        <v>4338.3</v>
+        <v>4426.3</v>
       </c>
       <c r="G21" s="102">
-        <v>4426.3</v>
+        <v>4480.1000000000004</v>
       </c>
       <c r="H21" s="103">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>53.800000000000182</v>
       </c>
       <c r="I21" s="104">
         <f t="shared" si="0"/>
-        <v>6.16</v>
+        <v>3.7660000000000129</v>
       </c>
       <c r="J21" s="114">
         <f t="shared" si="2"/>
-        <v>8253.2560000000012</v>
+        <v>5045.7406000000174</v>
       </c>
       <c r="K21" s="114">
         <f>K8*E21%</f>
-        <v>-17716.849178790002</v>
+        <v>9542.7428417000028</v>
       </c>
       <c r="L21" s="186">
         <f t="shared" si="3"/>
-        <v>33855.597338209998</v>
+        <v>61682.435246699992</v>
       </c>
       <c r="M21" s="105">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>53.800000000000182</v>
       </c>
       <c r="N21" s="103">
         <f t="shared" si="5"/>
-        <v>42108.853338209999</v>
+        <v>66728.175846700004</v>
       </c>
       <c r="O21" s="96">
         <f>N21+'prorrateo '!M14</f>
-        <v>224171.49067050699</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>215208.79190211699</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="97">
         <v>14</v>
       </c>
@@ -4772,45 +4778,43 @@
         <v>5.04</v>
       </c>
       <c r="F22" s="102">
-        <v>2797.6</v>
-      </c>
-      <c r="G22" s="102">
         <v>3145.8</v>
       </c>
+      <c r="G22" s="196"/>
       <c r="H22" s="103">
         <f t="shared" si="1"/>
-        <v>348.20000000000027</v>
+        <v>-3145.8</v>
       </c>
       <c r="I22" s="104">
         <f t="shared" si="0"/>
-        <v>24.37400000000002</v>
+        <v>-220.20600000000005</v>
       </c>
       <c r="J22" s="114">
         <f t="shared" si="2"/>
-        <v>32656.633400000028</v>
+        <v>-295035.14460000006</v>
       </c>
       <c r="K22" s="114">
         <f>K8*E22%</f>
-        <v>-17542.813332240003</v>
+        <v>9449.0027352000016</v>
       </c>
       <c r="L22" s="186">
         <f t="shared" si="3"/>
-        <v>33523.027619759996</v>
+        <v>61076.517415199996</v>
       </c>
       <c r="M22" s="105">
         <f t="shared" si="4"/>
-        <v>348.20000000000027</v>
+        <v>-3145.8</v>
       </c>
       <c r="N22" s="103">
         <f t="shared" si="5"/>
-        <v>66179.661019760024</v>
+        <v>-233958.62718480005</v>
       </c>
       <c r="O22" s="96">
         <f>N22+'prorrateo '!M15</f>
-        <v>509408.28225911758</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>130270.81977837184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="97">
         <v>15</v>
       </c>
@@ -4827,45 +4831,45 @@
         <v>5.21</v>
       </c>
       <c r="F23" s="102">
-        <v>5576.5</v>
+        <v>5835.3</v>
       </c>
       <c r="G23" s="102">
-        <v>5835.3</v>
+        <v>5974.2</v>
       </c>
       <c r="H23" s="103">
         <f t="shared" si="1"/>
-        <v>258.80000000000018</v>
+        <v>138.89999999999964</v>
       </c>
       <c r="I23" s="104">
         <f t="shared" si="0"/>
-        <v>18.116000000000014</v>
+        <v>9.7229999999999759</v>
       </c>
       <c r="J23" s="114">
         <f t="shared" si="2"/>
-        <v>24272.075600000018</v>
+        <v>13027.014299999966</v>
       </c>
       <c r="K23" s="114">
         <f>K8*E23%</f>
-        <v>-18134.535210510003</v>
+        <v>9767.7190973000033</v>
       </c>
       <c r="L23" s="186">
         <f t="shared" si="3"/>
-        <v>34653.764662490001</v>
+        <v>63136.638042300001</v>
       </c>
       <c r="M23" s="105">
         <f t="shared" si="4"/>
-        <v>258.80000000000018</v>
+        <v>138.89999999999964</v>
       </c>
       <c r="N23" s="103">
         <f t="shared" si="5"/>
-        <v>58925.840262490019</v>
+        <v>76163.65234229996</v>
       </c>
       <c r="O23" s="96">
         <f>N23+'prorrateo '!M16</f>
-        <v>261104.96454765362</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>228395.70519058354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="97">
         <v>16</v>
       </c>
@@ -4882,45 +4886,45 @@
         <v>5.04</v>
       </c>
       <c r="F24" s="102">
-        <v>1982.9</v>
+        <v>2020.8</v>
       </c>
       <c r="G24" s="102">
         <v>2020.8</v>
       </c>
       <c r="H24" s="103">
         <f t="shared" si="1"/>
-        <v>37.899999999999864</v>
+        <v>0</v>
       </c>
       <c r="I24" s="104">
         <f t="shared" si="0"/>
-        <v>2.6529999999999907</v>
+        <v>0</v>
       </c>
       <c r="J24" s="114">
         <f t="shared" si="2"/>
-        <v>3554.5272999999875</v>
+        <v>0</v>
       </c>
       <c r="K24" s="114">
         <f>K8*E24%</f>
-        <v>-17542.813332240003</v>
+        <v>9449.0027352000016</v>
       </c>
       <c r="L24" s="186">
         <f t="shared" si="3"/>
-        <v>33523.027619759996</v>
+        <v>61076.517415199996</v>
       </c>
       <c r="M24" s="105">
         <f t="shared" si="4"/>
-        <v>37.899999999999864</v>
+        <v>0</v>
       </c>
       <c r="N24" s="103">
         <f t="shared" si="5"/>
-        <v>37077.554919759983</v>
+        <v>61076.517415199996</v>
       </c>
       <c r="O24" s="96">
         <f>N24+'prorrateo '!M17</f>
-        <v>314447.41080647038</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>547847.99301161873</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="97">
         <v>17</v>
       </c>
@@ -4937,45 +4941,45 @@
         <v>5.21</v>
       </c>
       <c r="F25" s="102">
-        <v>2155.8000000000002</v>
+        <v>2317.3000000000002</v>
       </c>
       <c r="G25" s="102">
         <v>2317.3000000000002</v>
       </c>
       <c r="H25" s="103">
         <f t="shared" si="1"/>
-        <v>161.5</v>
+        <v>0</v>
       </c>
       <c r="I25" s="104">
         <f t="shared" si="0"/>
-        <v>11.305000000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="114">
         <f t="shared" si="2"/>
-        <v>15146.6005</v>
+        <v>0</v>
       </c>
       <c r="K25" s="114">
         <f>K8*E25%</f>
-        <v>-18134.535210510003</v>
+        <v>9767.7190973000033</v>
       </c>
       <c r="L25" s="186">
         <f t="shared" si="3"/>
-        <v>34653.764662490001</v>
+        <v>63136.638042300001</v>
       </c>
       <c r="M25" s="105">
         <f t="shared" si="4"/>
-        <v>161.5</v>
+        <v>0</v>
       </c>
       <c r="N25" s="103">
         <f t="shared" si="5"/>
-        <v>49800.365162490001</v>
+        <v>63136.638042300001</v>
       </c>
       <c r="O25" s="96">
         <f>N25+'prorrateo '!M18</f>
-        <v>242854.01228367997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>269526.5580433</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="97">
         <v>18</v>
       </c>
@@ -4992,65 +4996,65 @@
         <v>7.4</v>
       </c>
       <c r="F26" s="102">
-        <v>9974.5</v>
+        <v>10444</v>
       </c>
       <c r="G26" s="102">
         <v>10444</v>
       </c>
       <c r="H26" s="103">
         <f t="shared" si="1"/>
-        <v>469.5</v>
+        <v>0</v>
       </c>
       <c r="I26" s="104">
         <f t="shared" si="0"/>
-        <v>32.865000000000002</v>
+        <v>0</v>
       </c>
       <c r="J26" s="114">
         <f t="shared" si="2"/>
-        <v>44032.996500000001</v>
+        <v>0</v>
       </c>
       <c r="K26" s="114">
         <f>K8*E26%</f>
-        <v>-25757.305289400007</v>
+        <v>13873.535762000005</v>
       </c>
       <c r="L26" s="186">
         <f t="shared" si="3"/>
-        <v>49220.318330599999</v>
+        <v>89675.839061999985</v>
       </c>
       <c r="M26" s="105">
         <f t="shared" si="4"/>
-        <v>469.5</v>
+        <v>0</v>
       </c>
       <c r="N26" s="103">
         <f>J26+L26</f>
-        <v>93253.314830599993</v>
+        <v>89675.839061999985</v>
       </c>
       <c r="O26" s="96">
         <f>N26+'prorrateo '!M19</f>
-        <v>389975.78253919998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="193">
+        <v>382820.83100199996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="192">
         <v>19</v>
       </c>
-      <c r="B27" s="194">
+      <c r="B27" s="193">
         <v>19</v>
       </c>
       <c r="C27" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="195"/>
-      <c r="E27" s="196">
+      <c r="D27" s="194"/>
+      <c r="E27" s="195">
         <v>1.08</v>
       </c>
-      <c r="F27" s="197"/>
-      <c r="G27" s="197"/>
+      <c r="F27" s="196"/>
+      <c r="G27" s="196"/>
       <c r="H27" s="136">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="198">
+      <c r="I27" s="197">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5058,21 +5062,21 @@
       <c r="K27" s="188"/>
       <c r="L27" s="189">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M27" s="137">
         <v>0</v>
       </c>
       <c r="N27" s="136">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O27" s="96">
         <f>N27+'prorrateo '!M20</f>
-        <v>443443.71171734406</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>491853.46621922409</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="97">
         <v>20</v>
       </c>
@@ -5097,21 +5101,21 @@
       <c r="K28" s="114"/>
       <c r="L28" s="186">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M28" s="105">
         <v>0</v>
       </c>
       <c r="N28" s="103">
         <f t="shared" si="6"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O28" s="96">
         <f>N28+'prorrateo '!M21</f>
-        <v>44062.509824640001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>55871.148308400006</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="97"/>
       <c r="B29" s="89"/>
       <c r="C29" s="153" t="s">
@@ -5129,21 +5133,21 @@
       <c r="K29" s="114"/>
       <c r="L29" s="186">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M29" s="105">
         <v>0</v>
       </c>
       <c r="N29" s="103">
         <f t="shared" si="6"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O29" s="96">
         <f>N29+'prorrateo '!M22</f>
-        <v>44062.509824640001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>45330.613577999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="97"/>
       <c r="B30" s="89"/>
       <c r="C30" s="153" t="s">
@@ -5161,21 +5165,21 @@
       <c r="K30" s="114"/>
       <c r="L30" s="186">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M30" s="105">
         <v>0</v>
       </c>
       <c r="N30" s="103">
         <f t="shared" si="6"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O30" s="96">
         <f>N30+'prorrateo '!M23</f>
-        <v>44062.509824640001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>55871.148308400006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="97"/>
       <c r="B31" s="89"/>
       <c r="C31" s="153" t="s">
@@ -5195,21 +5199,21 @@
       <c r="K31" s="114"/>
       <c r="L31" s="186">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M31" s="105">
         <v>0</v>
       </c>
       <c r="N31" s="103">
         <f t="shared" si="6"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O31" s="96">
         <f>N31+'prorrateo '!M24</f>
-        <v>44062.509824640001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>55871.148308400006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="98"/>
       <c r="B32" s="171"/>
       <c r="C32" s="153" t="s">
@@ -5229,21 +5233,21 @@
       <c r="K32" s="114"/>
       <c r="L32" s="186">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M32" s="105">
         <v>0</v>
       </c>
       <c r="N32" s="103">
         <f t="shared" si="6"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O32" s="96">
         <f>N32+'prorrateo '!M25</f>
-        <v>44062.509824640001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>55871.148308400006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="97"/>
       <c r="B33" s="89"/>
       <c r="C33" s="127" t="s">
@@ -5263,21 +5267,21 @@
       <c r="K33" s="115"/>
       <c r="L33" s="186">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M33" s="105">
         <v>0</v>
       </c>
       <c r="N33" s="103">
         <f t="shared" si="6"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O33" s="96">
         <f>N33+'prorrateo '!M26</f>
-        <v>44062.509824640001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>55871.148308400006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="97"/>
       <c r="B34" s="89"/>
       <c r="C34" s="127" t="s">
@@ -5297,21 +5301,21 @@
       <c r="K34" s="115"/>
       <c r="L34" s="186">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M34" s="105">
         <v>0</v>
       </c>
       <c r="N34" s="103">
         <f t="shared" si="6"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O34" s="96">
         <f>N34+'prorrateo '!M27</f>
-        <v>44062.509824640001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>55871.148308400006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="97">
         <v>21</v>
       </c>
@@ -5336,21 +5340,21 @@
       <c r="K35" s="114"/>
       <c r="L35" s="186">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M35" s="105">
         <v>0</v>
       </c>
       <c r="N35" s="103">
         <f t="shared" si="6"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O35" s="96">
         <f>N35+'prorrateo '!M28</f>
-        <v>44062.509824640001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>55871.148308400006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="97">
         <v>22</v>
       </c>
@@ -5377,21 +5381,21 @@
       <c r="K36" s="114"/>
       <c r="L36" s="186">
         <f t="shared" si="3"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="M36" s="105">
         <v>0</v>
       </c>
       <c r="N36" s="103">
         <f t="shared" si="6"/>
-        <v>7183.5059185199998</v>
+        <v>13087.825160400002</v>
       </c>
       <c r="O36" s="96">
         <f>N36+'prorrateo '!M29</f>
-        <v>93089.826603100781</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>144924.71841684403</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="97">
         <v>23</v>
       </c>
@@ -5421,7 +5425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="97">
         <v>24</v>
       </c>
@@ -5435,21 +5439,21 @@
       <c r="I38" s="110"/>
       <c r="J38" s="115">
         <f>SUM(J10:J37)</f>
-        <v>348071.69310000003</v>
+        <v>-187480.21300000005</v>
       </c>
       <c r="K38" s="111"/>
       <c r="L38" s="111">
         <f>SUM(L10:L37)</f>
-        <v>665139.43690000044</v>
+        <v>1211835.6630000002</v>
       </c>
       <c r="M38" s="112"/>
       <c r="N38" s="108">
         <f>SUM(N10:N37)</f>
-        <v>1013211.1300000006</v>
+        <v>1024355.4500000002</v>
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
       <c r="C39" s="90"/>
       <c r="D39" s="91"/>
@@ -5462,53 +5466,53 @@
       <c r="H39" s="92"/>
       <c r="I39" s="93">
         <f>SUM(I10:I38)</f>
-        <v>259.79100000000005</v>
+        <v>-139.93000000000004</v>
       </c>
       <c r="J39" s="123"/>
       <c r="K39" s="93"/>
       <c r="L39" s="130">
         <f>L38+J38</f>
-        <v>1013211.1300000005</v>
+        <v>1024355.4500000002</v>
       </c>
       <c r="M39" s="92"/>
       <c r="N39" s="92"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="212"/>
-      <c r="D40" s="210"/>
-      <c r="E40" s="210"/>
-      <c r="F40" s="210"/>
-      <c r="G40" s="210"/>
-      <c r="H40" s="210"/>
-      <c r="I40" s="210"/>
-      <c r="J40" s="210"/>
-      <c r="K40" s="210"/>
-      <c r="L40" s="210"/>
-      <c r="M40" s="210"/>
-      <c r="N40" s="210"/>
+      <c r="C40" s="210"/>
+      <c r="D40" s="208"/>
+      <c r="E40" s="208"/>
+      <c r="F40" s="208"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
       <c r="O40" s="94"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="79"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
       <c r="L41" s="95"/>
       <c r="N41" s="96"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="138"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="95"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="139"/>
       <c r="F46" s="139"/>
       <c r="G46" s="139"/>

--- a/2026/ROSALES/Marzo/expensas rosales Marzo.xlsx
+++ b/2026/ROSALES/Marzo/expensas rosales Marzo.xlsx
@@ -1,38 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ROSALES\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ROSALES\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57560F36-23B0-47DD-870A-5B436F4E06F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F9DCF9-DB78-451C-9021-04F1FB897679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
+    <sheet name="SITUACION ARIEL" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'SITUACION ARIEL'!$D$4:$H$20</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="132">
   <si>
     <t>TOTAL</t>
   </si>
@@ -399,6 +396,36 @@
   </si>
   <si>
     <t>Fumigacion - Mes anterior</t>
+  </si>
+  <si>
+    <t>En Febrero debia abonar:</t>
+  </si>
+  <si>
+    <t>9A</t>
+  </si>
+  <si>
+    <t>Cochera 7</t>
+  </si>
+  <si>
+    <t>Cochera 8</t>
+  </si>
+  <si>
+    <t>Abona:</t>
+  </si>
+  <si>
+    <t>Portera</t>
+  </si>
+  <si>
+    <t>TOTAL AL FINALIZAR FEBRERO (DEUDA)</t>
+  </si>
+  <si>
+    <t>En marzo debia abonar:</t>
+  </si>
+  <si>
+    <t>TOTAL + DEUDA FEB</t>
+  </si>
+  <si>
+    <t>Gastos administrativos - Traspaso de administracion</t>
   </si>
 </sst>
 </file>
@@ -1024,7 +1051,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1235,8 +1262,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="25" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1244,9 +1269,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1317,8 +1339,6 @@
     <xf numFmtId="171" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="28" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1331,14 +1351,16 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="26" fillId="6" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="26" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1371,9 +1393,8 @@
     <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1503,9 +1524,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1543,9 +1564,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1578,26 +1599,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1630,26 +1634,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1826,17 +1813,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:F64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1844,22 +1831,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
@@ -1870,425 +1857,436 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="212" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="28" t="s">
         <v>102</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="199">
+      <c r="C18" s="33">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="212" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="198">
+      <c r="C19" s="193">
         <v>372886.04</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="212" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="199">
+      <c r="C20" s="33">
         <v>85000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="212" t="s">
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="28" t="s">
         <v>120</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="199">
+      <c r="C21" s="33">
         <v>1034026.5</v>
       </c>
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="212" t="s">
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="39"/>
+      <c r="C22" s="33">
+        <v>200000</v>
+      </c>
+      <c r="D22" s="20"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B23" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="199">
+      <c r="C23" s="33">
         <v>89200</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F23" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="40"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="23">
-        <f>SUM(C17:C22)</f>
-        <v>1657766.54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="40"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="23">
+        <f>SUM(C17:C23)</f>
+        <v>1857766.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="178"/>
-      <c r="D24" s="45"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="B25" s="39"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="45"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="199">
+      <c r="B26" s="42"/>
+      <c r="C26" s="33">
         <f>384067+ (384067*3%)</f>
         <v>395589.01</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="199">
-        <v>7458</v>
-      </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="42"/>
+        <v>97</v>
+      </c>
+      <c r="B27" s="28"/>
       <c r="C27" s="33">
-        <v>0</v>
+        <v>7458</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="28" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B28" s="42"/>
-      <c r="C28" s="213">
-        <v>55000</v>
+      <c r="C28" s="33">
+        <v>0</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="194">
+        <v>55000</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="213">
+      <c r="B30" s="42"/>
+      <c r="C30" s="194">
         <v>55000</v>
       </c>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="40"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="23">
-        <f>SUM(C24:C30)</f>
+      <c r="B31" s="39"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="40"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="23">
+        <f>SUM(C25:C31)</f>
         <v>513047.01</v>
       </c>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="43">
-        <f>+C31+C23</f>
-        <v>2170813.5499999998</v>
-      </c>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C33" s="24"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="43">
+        <f>+C32+C24</f>
+        <v>2370813.5499999998</v>
+      </c>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>17</v>
-      </c>
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="173"/>
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="24"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
-      <c r="C36" s="173"/>
+      <c r="C36" s="170"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
-      <c r="C37" s="34"/>
+      <c r="C37" s="170"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C38" s="25"/>
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="34"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="157" t="s">
+    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C39" s="25"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="157"/>
-      <c r="C39" s="158">
-        <v>0</v>
-      </c>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C40" s="25"/>
+      <c r="B40" s="154"/>
+      <c r="C40" s="155">
+        <v>0</v>
+      </c>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
+    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C41" s="25"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14">
-        <f>+C35+C36+C37+C40</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="6"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="B42" s="13"/>
+      <c r="C42" s="14">
+        <f>+C36+C37+C38+C41</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="19">
-        <f>+C41+C32</f>
-        <v>2170813.5499999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-      <c r="C45" s="141"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="163" t="s">
-        <v>98</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="164">
-        <v>1039280.7042474523</v>
-      </c>
+      <c r="B44" s="18"/>
+      <c r="C44" s="19">
+        <f>+C42+C33</f>
+        <v>2370813.5499999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="C46" s="139"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="163" t="s">
-        <v>119</v>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="160" t="s">
+        <v>98</v>
       </c>
       <c r="B47" s="28"/>
-      <c r="C47" s="177">
-        <f>-(C43-C30)</f>
-        <v>-2170813.5499999998</v>
+      <c r="C47" s="161">
+        <v>1039280.7042474523</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="163" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="160" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="174">
+        <f>-(C44-C31)</f>
+        <v>-2370813.5499999998</v>
+      </c>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="160" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="165">
+      <c r="B49" s="28"/>
+      <c r="C49" s="162">
         <f>'prorrateo '!F31</f>
-        <v>3584406.0490640621</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="163" t="s">
+        <v>3661916.314806771</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="160" t="s">
         <v>110</v>
       </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="176">
+      <c r="B50" s="28"/>
+      <c r="C50" s="173">
         <v>-1024355.45</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="163" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="160" t="s">
         <v>109</v>
       </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="163" t="s">
+      <c r="B51" s="28"/>
+      <c r="C51" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="164">
-        <f>SUM(C46:C50)</f>
-        <v>1428517.7533115146</v>
-      </c>
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="9"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="10"/>
-    </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="200"/>
-      <c r="B53" s="200"/>
-      <c r="C53" s="200"/>
-      <c r="F53" s="44"/>
-    </row>
-    <row r="54" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="201"/>
-      <c r="B54" s="201"/>
-      <c r="C54" s="201"/>
-    </row>
-    <row r="55" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="26" t="s">
+      <c r="B52" s="28"/>
+      <c r="C52" s="161">
+        <f>SUM(C47:C51)</f>
+        <v>1306028.0190542236</v>
+      </c>
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="9"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="10"/>
+    </row>
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="195"/>
+      <c r="B54" s="195"/>
+      <c r="C54" s="195"/>
+      <c r="F54" s="44"/>
+    </row>
+    <row r="55" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="196"/>
+      <c r="B55" s="196"/>
+      <c r="C55" s="196"/>
+    </row>
+    <row r="56" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="29"/>
-    </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="28" t="s">
+      <c r="B56" s="27"/>
+      <c r="C56" s="29"/>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="31">
-        <f>-C41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="28"/>
       <c r="B57" s="28"/>
-      <c r="C57" s="31"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="31">
+        <f>-C42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="28"/>
       <c r="B58" s="28"/>
-      <c r="C58" s="32"/>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="142" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="143"/>
-      <c r="C59" s="144">
-        <f>SUM(C55:C58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="202" t="s">
+      <c r="C58" s="31"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="32"/>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="140" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="141"/>
+      <c r="C60" s="142">
+        <f>SUM(C56:C59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="197" t="s">
         <v>105</v>
       </c>
-      <c r="B60" s="203"/>
-      <c r="C60" s="203"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="203"/>
-      <c r="B61" s="203"/>
-      <c r="C61" s="203"/>
-    </row>
-    <row r="62" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="203"/>
-      <c r="B62" s="203"/>
-      <c r="C62" s="203"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
+      <c r="B61" s="198"/>
+      <c r="C61" s="198"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="198"/>
+      <c r="B62" s="198"/>
+      <c r="C62" s="198"/>
+    </row>
+    <row r="63" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="198"/>
+      <c r="B63" s="198"/>
+      <c r="C63" s="198"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A53:C54"/>
-    <mergeCell ref="A60:C62"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A61:C63"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2296,7 +2294,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="88" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -2307,58 +2305,62 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="10" width="10.6640625" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="11" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="204">
-        <f>N1</f>
-        <v>2249583.1469999999</v>
-      </c>
-      <c r="C1" s="204"/>
+      <c r="B1" s="199">
+        <f>N1-L1</f>
+        <v>1336787.0499999998</v>
+      </c>
+      <c r="C1" s="199"/>
       <c r="D1" s="135">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="205">
-        <v>0</v>
-      </c>
-      <c r="H1" s="205"/>
-      <c r="I1" s="206" t="s">
+      <c r="G1" s="200">
+        <v>0</v>
+      </c>
+      <c r="H1" s="200"/>
+      <c r="I1" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="204">
-        <v>500000</v>
-      </c>
-      <c r="M1" s="204"/>
+      <c r="J1" s="201"/>
+      <c r="K1" s="201"/>
+      <c r="L1" s="199">
+        <f>O1</f>
+        <v>1034026.5</v>
+      </c>
+      <c r="M1" s="199"/>
       <c r="N1">
-        <v>2249583.1469999999</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2370813.5499999998</v>
+      </c>
+      <c r="O1" s="11">
+        <v>1034026.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2380,7 +2382,7 @@
       <c r="G2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="162" t="s">
+      <c r="H2" s="159" t="s">
         <v>92</v>
       </c>
       <c r="I2" s="50" t="s">
@@ -2402,7 +2404,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2418,11 +2420,11 @@
       <c r="E3" s="126">
         <v>196577.35914129001</v>
       </c>
-      <c r="F3" s="175">
+      <c r="F3" s="172">
         <f t="shared" ref="F3" si="0">E3</f>
         <v>196577.35914129001</v>
       </c>
-      <c r="G3" s="181">
+      <c r="G3" s="178">
         <f>E3-F3</f>
         <v>0</v>
       </c>
@@ -2432,11 +2434,11 @@
       </c>
       <c r="I3" s="56">
         <f>B$1*D3/100</f>
-        <v>114953.69881170001</v>
+        <v>68309.818254999991</v>
       </c>
       <c r="J3" s="56">
         <f>Edesur!N10</f>
-        <v>70956.490479300017</v>
+        <v>54290.037880980017</v>
       </c>
       <c r="K3" s="56">
         <f>G$1*D3/100</f>
@@ -2444,19 +2446,19 @@
       </c>
       <c r="L3" s="56">
         <f>L$1*D3/100</f>
-        <v>25550</v>
+        <v>52838.754150000001</v>
       </c>
       <c r="M3" s="57">
         <f>I3+G3+L3+K3+H3+J3</f>
-        <v>211460.18929100002</v>
+        <v>175438.61028597999</v>
       </c>
       <c r="N3" s="44"/>
-      <c r="O3" s="138">
+      <c r="O3" s="136">
         <f>M3-J3</f>
-        <v>140503.69881169999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>121148.57240499997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2470,24 +2472,22 @@
       <c r="E4" s="126">
         <v>305245.8364308484</v>
       </c>
-      <c r="F4" s="175">
-        <v>110474</v>
-      </c>
-      <c r="G4" s="181">
+      <c r="F4" s="172"/>
+      <c r="G4" s="178">
         <f t="shared" ref="G4:G29" si="1">E4-F4</f>
-        <v>194771.8364308484</v>
+        <v>305245.8364308484</v>
       </c>
       <c r="H4" s="56">
         <f t="shared" ref="H4:H29" si="2">IF(G4&gt;0,G4*4%,0)</f>
-        <v>7790.8734572339363</v>
+        <v>12209.833457233935</v>
       </c>
       <c r="I4" s="56">
         <f t="shared" ref="I4:I29" si="3">B$1*D4/100</f>
-        <v>114503.7821823</v>
+        <v>68042.460844999994</v>
       </c>
       <c r="J4" s="56">
         <f>Edesur!N11</f>
-        <v>61860.630546699955</v>
+        <v>45259.408682619964</v>
       </c>
       <c r="K4" s="56">
         <f t="shared" ref="K4:K29" si="4">G$1*D4/100</f>
@@ -2495,19 +2495,19 @@
       </c>
       <c r="L4" s="56">
         <f t="shared" ref="L4:L29" si="5">L$1*D4/100</f>
-        <v>25450</v>
+        <v>52631.948850000001</v>
       </c>
       <c r="M4" s="57">
         <f t="shared" ref="M4:M29" si="6">I4+G4+L4+K4+H4+J4</f>
-        <v>404377.12261708232</v>
+        <v>483389.48826570227</v>
       </c>
       <c r="N4" s="44"/>
-      <c r="O4" s="138">
+      <c r="O4" s="136">
         <f t="shared" ref="O4:O29" si="7">M4-J4</f>
-        <v>342516.49207038234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>438130.07958308229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2521,13 +2521,13 @@
       <c r="E5" s="126">
         <v>204343.43875076872</v>
       </c>
-      <c r="F5" s="175">
-        <f>301940.37-F23</f>
-        <v>265339.25398188003</v>
-      </c>
-      <c r="G5" s="181">
+      <c r="F5" s="172">
+        <f>240944.56-F23</f>
+        <v>240944.56</v>
+      </c>
+      <c r="G5" s="178">
         <f t="shared" si="1"/>
-        <v>-60995.815231111308</v>
+        <v>-36601.121249231277</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="2"/>
@@ -2535,11 +2535,11 @@
       </c>
       <c r="I5" s="56">
         <f t="shared" si="3"/>
-        <v>113378.9906088</v>
+        <v>67374.067319999987</v>
       </c>
       <c r="J5" s="56">
         <f>Edesur!N12</f>
-        <v>70267.6434152</v>
+        <v>53829.498386719992</v>
       </c>
       <c r="K5" s="56">
         <f t="shared" si="4"/>
@@ -2547,37 +2547,37 @@
       </c>
       <c r="L5" s="56">
         <f t="shared" si="5"/>
-        <v>25200</v>
+        <v>52114.935599999997</v>
       </c>
       <c r="M5" s="57">
         <f t="shared" si="6"/>
-        <v>147850.81879288869</v>
+        <v>136717.38005748868</v>
       </c>
       <c r="N5" s="44"/>
-      <c r="O5" s="138">
+      <c r="O5" s="136">
         <f t="shared" si="7"/>
-        <v>77583.175377688691</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>82887.881670768693</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="161"/>
+      <c r="B6" s="158"/>
       <c r="C6" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="160">
+      <c r="D6" s="157">
         <v>5.21</v>
       </c>
       <c r="E6" s="126">
         <v>188205.46156518997</v>
       </c>
-      <c r="F6" s="175">
+      <c r="F6" s="172">
         <f>E6</f>
         <v>188205.46156518997</v>
       </c>
-      <c r="G6" s="182">
+      <c r="G6" s="179">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2587,11 +2587,11 @@
       </c>
       <c r="I6" s="64">
         <f t="shared" si="3"/>
-        <v>117203.28195869998</v>
+        <v>69646.60530499999</v>
       </c>
       <c r="J6" s="64">
         <f>Edesur!N13</f>
-        <v>68548.147942300013</v>
+        <v>51555.541672780004</v>
       </c>
       <c r="K6" s="64">
         <f t="shared" si="4"/>
@@ -2599,19 +2599,19 @@
       </c>
       <c r="L6" s="64">
         <f t="shared" si="5"/>
-        <v>26050</v>
-      </c>
-      <c r="M6" s="174">
+        <v>53872.780650000001</v>
+      </c>
+      <c r="M6" s="171">
         <f t="shared" si="6"/>
-        <v>211801.429901</v>
-      </c>
-      <c r="O6" s="138">
+        <v>175074.92762778001</v>
+      </c>
+      <c r="O6" s="136">
         <f t="shared" si="7"/>
-        <v>143253.28195869998</v>
-      </c>
-      <c r="P6" s="159"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>123519.38595500001</v>
+      </c>
+      <c r="P6" s="156"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2627,13 +2627,13 @@
       <c r="E7" s="126">
         <v>199212.77119878004</v>
       </c>
-      <c r="F7" s="175">
-        <f>199250.14+92850-F28</f>
-        <v>255499.02398188002</v>
-      </c>
-      <c r="G7" s="181">
+      <c r="F7" s="172">
+        <f>235813.89-F28</f>
+        <v>199212.77398188002</v>
+      </c>
+      <c r="G7" s="178">
         <f t="shared" si="1"/>
-        <v>-56286.252783099975</v>
+        <v>-2.7830999752040952E-3</v>
       </c>
       <c r="H7" s="56">
         <f t="shared" si="2"/>
@@ -2641,11 +2641,11 @@
       </c>
       <c r="I7" s="56">
         <f t="shared" si="3"/>
-        <v>114953.69881170001</v>
+        <v>68309.818254999991</v>
       </c>
       <c r="J7" s="56">
         <f>Edesur!N14</f>
-        <v>73516.875579300031</v>
+        <v>56850.422980980038</v>
       </c>
       <c r="K7" s="56">
         <f t="shared" si="4"/>
@@ -2653,19 +2653,19 @@
       </c>
       <c r="L7" s="56">
         <f t="shared" si="5"/>
-        <v>25550</v>
+        <v>52838.754150000001</v>
       </c>
       <c r="M7" s="57">
         <f t="shared" si="6"/>
-        <v>157734.32160790008</v>
-      </c>
-      <c r="O7" s="138">
+        <v>177998.99260288005</v>
+      </c>
+      <c r="O7" s="136">
         <f t="shared" si="7"/>
-        <v>84217.446028600054</v>
-      </c>
-      <c r="P7" s="159"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>121148.56962190001</v>
+      </c>
+      <c r="P7" s="156"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="E8" s="126">
         <v>202248.94059650999</v>
       </c>
-      <c r="F8" s="175">
+      <c r="F8" s="172">
         <f t="shared" ref="F8" si="8">E8</f>
         <v>202248.94059650999</v>
       </c>
-      <c r="G8" s="181">
+      <c r="G8" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2693,11 +2693,11 @@
       </c>
       <c r="I8" s="56">
         <f t="shared" si="3"/>
-        <v>114503.7821823</v>
+        <v>68042.460844999994</v>
       </c>
       <c r="J8" s="56">
         <f>Edesur!N15</f>
-        <v>69204.152646699979</v>
+        <v>52602.93078261998</v>
       </c>
       <c r="K8" s="56">
         <f t="shared" si="4"/>
@@ -2705,18 +2705,18 @@
       </c>
       <c r="L8" s="56">
         <f t="shared" si="5"/>
-        <v>25450</v>
+        <v>52631.948850000001</v>
       </c>
       <c r="M8" s="57">
         <f t="shared" si="6"/>
-        <v>209157.93482899998</v>
-      </c>
-      <c r="O8" s="138">
+        <v>173277.34047761996</v>
+      </c>
+      <c r="O8" s="136">
         <f t="shared" si="7"/>
-        <v>139953.7821823</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>120674.40969499998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2730,11 +2730,11 @@
       <c r="E9" s="126">
         <v>186016.94294129004</v>
       </c>
-      <c r="F9" s="175">
+      <c r="F9" s="172">
         <f>E9</f>
         <v>186016.94294129004</v>
       </c>
-      <c r="G9" s="181">
+      <c r="G9" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2744,11 +2744,11 @@
       </c>
       <c r="I9" s="56">
         <f t="shared" si="3"/>
-        <v>114953.69881170001</v>
+        <v>68309.818254999991</v>
       </c>
       <c r="J9" s="56">
         <f>Edesur!N16</f>
-        <v>69615.336379300003</v>
+        <v>52948.883780980002</v>
       </c>
       <c r="K9" s="56">
         <f t="shared" si="4"/>
@@ -2756,48 +2756,48 @@
       </c>
       <c r="L9" s="56">
         <f t="shared" si="5"/>
-        <v>25550</v>
+        <v>52838.754150000001</v>
       </c>
       <c r="M9" s="57">
         <f t="shared" si="6"/>
-        <v>210119.03519100003</v>
-      </c>
-      <c r="O9" s="138">
+        <v>174097.45618598</v>
+      </c>
+      <c r="O9" s="136">
         <f t="shared" si="7"/>
-        <v>140503.69881170004</v>
-      </c>
-      <c r="P9" s="159"/>
-    </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="190" t="s">
+        <v>121148.572405</v>
+      </c>
+      <c r="P9" s="156"/>
+    </row>
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="191"/>
+      <c r="B10" s="186"/>
       <c r="C10" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="160">
+      <c r="D10" s="157">
         <v>5.09</v>
       </c>
       <c r="E10" s="126">
         <v>176391.66853574003</v>
       </c>
-      <c r="F10" s="175">
-        <f>379452.66-107386-F22</f>
-        <v>224925.00925147996</v>
-      </c>
-      <c r="G10" s="182">
+      <c r="F10" s="172">
+        <f>212992.98-F22</f>
+        <v>176391.86398188001</v>
+      </c>
+      <c r="G10" s="179">
         <f t="shared" si="1"/>
-        <v>-48533.340715739934</v>
+        <v>-0.1954461399873253</v>
       </c>
       <c r="H10" s="64"/>
       <c r="I10" s="64">
         <f t="shared" si="3"/>
-        <v>114503.7821823</v>
+        <v>68042.460844999994</v>
       </c>
       <c r="J10" s="64">
         <f>Edesur!N17</f>
-        <v>63164.269846700008</v>
+        <v>46563.047982620017</v>
       </c>
       <c r="K10" s="64">
         <f t="shared" si="4"/>
@@ -2805,18 +2805,18 @@
       </c>
       <c r="L10" s="64">
         <f t="shared" si="5"/>
-        <v>25450</v>
-      </c>
-      <c r="M10" s="174">
+        <v>52631.948850000001</v>
+      </c>
+      <c r="M10" s="171">
         <f t="shared" si="6"/>
-        <v>154584.71131326008</v>
-      </c>
-      <c r="O10" s="138">
+        <v>167237.26223148004</v>
+      </c>
+      <c r="O10" s="136">
         <f t="shared" si="7"/>
-        <v>91420.441466560063</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>120674.21424886002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>94</v>
       </c>
@@ -2830,11 +2830,11 @@
       <c r="E11" s="126">
         <v>182106.54158456001</v>
       </c>
-      <c r="F11" s="175">
+      <c r="F11" s="172">
         <f>E11</f>
         <v>182106.54158456001</v>
       </c>
-      <c r="G11" s="181">
+      <c r="G11" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2844,11 +2844,11 @@
       </c>
       <c r="I11" s="56">
         <f t="shared" si="3"/>
-        <v>113378.9906088</v>
+        <v>67374.067319999987</v>
       </c>
       <c r="J11" s="56">
         <f>Edesur!N18</f>
-        <v>66778.767015199977</v>
+        <v>50340.621986719969</v>
       </c>
       <c r="K11" s="56">
         <f t="shared" si="4"/>
@@ -2856,18 +2856,18 @@
       </c>
       <c r="L11" s="56">
         <f t="shared" si="5"/>
-        <v>25200</v>
+        <v>52114.935599999997</v>
       </c>
       <c r="M11" s="57">
         <f t="shared" si="6"/>
-        <v>205357.75762399996</v>
-      </c>
-      <c r="O11" s="138">
+        <v>169829.62490671995</v>
+      </c>
+      <c r="O11" s="136">
         <f t="shared" si="7"/>
-        <v>138578.99060879997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>119489.00291999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2881,11 +2881,11 @@
       <c r="E12" s="126">
         <v>211989.84476518998</v>
       </c>
-      <c r="F12" s="175">
+      <c r="F12" s="172">
         <f t="shared" ref="F12" si="9">E12</f>
         <v>211989.84476518998</v>
       </c>
-      <c r="G12" s="181">
+      <c r="G12" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2895,11 +2895,11 @@
       </c>
       <c r="I12" s="56">
         <f t="shared" si="3"/>
-        <v>117203.28195869998</v>
+        <v>69646.60530499999</v>
       </c>
       <c r="J12" s="56">
         <f>Edesur!N19</f>
-        <v>79933.889742300031</v>
+        <v>62941.283472780036</v>
       </c>
       <c r="K12" s="56">
         <f t="shared" si="4"/>
@@ -2907,18 +2907,18 @@
       </c>
       <c r="L12" s="56">
         <f t="shared" si="5"/>
-        <v>26050</v>
+        <v>53872.780650000001</v>
       </c>
       <c r="M12" s="57">
         <f t="shared" si="6"/>
-        <v>223187.17170100001</v>
-      </c>
-      <c r="O12" s="138">
+        <v>186460.66942778003</v>
+      </c>
+      <c r="O12" s="136">
         <f t="shared" si="7"/>
-        <v>143253.28195869998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>123519.38595499999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2934,25 +2934,25 @@
       <c r="E13" s="126">
         <v>205111.98067307967</v>
       </c>
-      <c r="F13" s="175">
-        <f>300766.05-F24</f>
-        <v>264164.93398187996</v>
-      </c>
-      <c r="G13" s="181">
+      <c r="F13" s="172">
+        <f>241713-F24</f>
+        <v>205111.88398188</v>
+      </c>
+      <c r="G13" s="178">
         <f t="shared" si="1"/>
-        <v>-59052.953308800294</v>
+        <v>9.6691199665656313E-2</v>
       </c>
       <c r="H13" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.8676479866262526E-3</v>
       </c>
       <c r="I13" s="56">
         <f t="shared" si="3"/>
-        <v>114953.69881170001</v>
+        <v>68309.818254999991</v>
       </c>
       <c r="J13" s="56">
         <f>Edesur!N20</f>
-        <v>76808.799279299972</v>
+        <v>60142.346680979987</v>
       </c>
       <c r="K13" s="56">
         <f t="shared" si="4"/>
@@ -2960,53 +2960,50 @@
       </c>
       <c r="L13" s="56">
         <f t="shared" si="5"/>
-        <v>25550</v>
+        <v>52838.754150000001</v>
       </c>
       <c r="M13" s="57">
         <f t="shared" si="6"/>
-        <v>158259.54478219969</v>
+        <v>181291.01964482764</v>
       </c>
       <c r="N13" s="44"/>
-      <c r="O13" s="138">
+      <c r="O13" s="136">
         <f t="shared" si="7"/>
-        <v>81450.745502899721</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>121148.67296384765</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="161" t="s">
+      <c r="B14" s="158" t="s">
         <v>103</v>
       </c>
       <c r="C14" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="160">
+      <c r="D14" s="157">
         <v>5.09</v>
       </c>
       <c r="E14" s="126">
         <v>180752.96200829698</v>
       </c>
-      <c r="F14" s="175">
-        <f>275555.42-F25</f>
-        <v>238954.30398187999</v>
-      </c>
-      <c r="G14" s="182">
+      <c r="F14" s="172"/>
+      <c r="G14" s="179">
         <f t="shared" si="1"/>
-        <v>-58201.34197358301</v>
+        <v>180752.96200829698</v>
       </c>
       <c r="H14" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7230.1184803318793</v>
       </c>
       <c r="I14" s="64">
         <f t="shared" si="3"/>
-        <v>114503.7821823</v>
+        <v>68042.460844999994</v>
       </c>
       <c r="J14" s="56">
         <f>Edesur!N21</f>
-        <v>66728.175846700004</v>
+        <v>50126.95398262002</v>
       </c>
       <c r="K14" s="64">
         <f t="shared" si="4"/>
@@ -3014,18 +3011,18 @@
       </c>
       <c r="L14" s="56">
         <f t="shared" si="5"/>
-        <v>25450</v>
+        <v>52631.948850000001</v>
       </c>
       <c r="M14" s="57">
         <f t="shared" si="6"/>
-        <v>148480.61605541699</v>
-      </c>
-      <c r="O14" s="138">
+        <v>358784.4441662489</v>
+      </c>
+      <c r="O14" s="136">
         <f t="shared" si="7"/>
-        <v>81752.440208716987</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>308657.49018362886</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3041,22 +3038,25 @@
       <c r="E15" s="126">
         <v>441931.81109535758</v>
       </c>
-      <c r="F15" s="175"/>
-      <c r="G15" s="181">
+      <c r="F15" s="172">
+        <f>490000-F29</f>
+        <v>404371.56720341922</v>
+      </c>
+      <c r="G15" s="178">
         <f t="shared" si="1"/>
-        <v>441931.81109535758</v>
+        <v>37560.243891938357</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="2"/>
-        <v>17677.272443814305</v>
+        <v>1502.4097556775343</v>
       </c>
       <c r="I15" s="56">
         <f t="shared" si="3"/>
-        <v>113378.9906088</v>
+        <v>67374.067319999987</v>
       </c>
       <c r="J15" s="56">
         <f>Edesur!N22</f>
-        <v>-233958.62718480005</v>
+        <v>55808.404086719987</v>
       </c>
       <c r="K15" s="56">
         <f t="shared" si="4"/>
@@ -3064,18 +3064,18 @@
       </c>
       <c r="L15" s="56">
         <f t="shared" si="5"/>
-        <v>25200</v>
+        <v>52114.935599999997</v>
       </c>
       <c r="M15" s="57">
         <f t="shared" si="6"/>
-        <v>364229.44696317188</v>
-      </c>
-      <c r="O15" s="138">
+        <v>214360.06065433589</v>
+      </c>
+      <c r="O15" s="136">
         <f t="shared" si="7"/>
-        <v>598188.07414797193</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>158551.65656761589</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3091,13 +3091,13 @@
       <c r="E16" s="126">
         <v>200838.57252916362</v>
       </c>
-      <c r="F16" s="175">
-        <f>304624.57-F21</f>
-        <v>268023.45398187998</v>
-      </c>
-      <c r="G16" s="181">
+      <c r="F16" s="172">
+        <f>237500-F21</f>
+        <v>200898.88398188</v>
+      </c>
+      <c r="G16" s="178">
         <f t="shared" si="1"/>
-        <v>-67184.881452716363</v>
+        <v>-60.311452716385247</v>
       </c>
       <c r="H16" s="56">
         <f t="shared" si="2"/>
@@ -3105,11 +3105,11 @@
       </c>
       <c r="I16" s="56">
         <f t="shared" si="3"/>
-        <v>117203.28195869998</v>
+        <v>69646.60530499999</v>
       </c>
       <c r="J16" s="56">
         <f>Edesur!N23</f>
-        <v>76163.65234229996</v>
+        <v>59171.046072779965</v>
       </c>
       <c r="K16" s="56">
         <f t="shared" si="4"/>
@@ -3117,19 +3117,19 @@
       </c>
       <c r="L16" s="56">
         <f t="shared" si="5"/>
-        <v>26050</v>
+        <v>53872.780650000001</v>
       </c>
       <c r="M16" s="57">
         <f t="shared" si="6"/>
-        <v>152232.05284828358</v>
+        <v>182630.12057506357</v>
       </c>
       <c r="N16" s="44"/>
-      <c r="O16" s="138">
+      <c r="O16" s="136">
         <f t="shared" si="7"/>
-        <v>76068.40050598362</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>123459.07450228361</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3143,22 +3143,25 @@
       <c r="E17" s="126">
         <v>276073.04574271035</v>
       </c>
-      <c r="F17" s="175"/>
-      <c r="G17" s="181">
+      <c r="F17" s="172">
+        <f>E17</f>
+        <v>276073.04574271035</v>
+      </c>
+      <c r="G17" s="178">
         <f t="shared" si="1"/>
-        <v>276073.04574271035</v>
+        <v>0</v>
       </c>
       <c r="H17" s="56">
         <f t="shared" si="2"/>
-        <v>11042.921829708413</v>
+        <v>0</v>
       </c>
       <c r="I17" s="56">
         <f t="shared" si="3"/>
-        <v>113378.9906088</v>
+        <v>67374.067319999987</v>
       </c>
       <c r="J17" s="56">
         <f>Edesur!N24</f>
-        <v>61076.517415199996</v>
+        <v>46701.686386719994</v>
       </c>
       <c r="K17" s="56">
         <f t="shared" si="4"/>
@@ -3166,36 +3169,36 @@
       </c>
       <c r="L17" s="56">
         <f t="shared" si="5"/>
-        <v>25200</v>
+        <v>52114.935599999997</v>
       </c>
       <c r="M17" s="57">
         <f t="shared" si="6"/>
-        <v>486771.47559641872</v>
-      </c>
-      <c r="O17" s="138">
+        <v>166190.68930671999</v>
+      </c>
+      <c r="O17" s="136">
         <f t="shared" si="7"/>
-        <v>425694.95818121871</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="167" t="s">
+        <v>119489.00292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="168"/>
+      <c r="B18" s="165"/>
       <c r="C18" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="160">
+      <c r="D18" s="157">
         <v>5.21</v>
       </c>
       <c r="E18" s="126">
         <v>191713.09536518998</v>
       </c>
-      <c r="F18" s="175">
+      <c r="F18" s="172">
         <f t="shared" ref="F18:F21" si="10">E18</f>
         <v>191713.09536518998</v>
       </c>
-      <c r="G18" s="182">
+      <c r="G18" s="179">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3205,11 +3208,11 @@
       </c>
       <c r="I18" s="64">
         <f t="shared" si="3"/>
-        <v>117203.28195869998</v>
+        <v>69646.60530499999</v>
       </c>
       <c r="J18" s="56">
         <f>Edesur!N25</f>
-        <v>63136.638042300001</v>
+        <v>52333.973772780002</v>
       </c>
       <c r="K18" s="64">
         <f t="shared" si="4"/>
@@ -3217,39 +3220,39 @@
       </c>
       <c r="L18" s="64">
         <f t="shared" si="5"/>
-        <v>26050</v>
+        <v>53872.780650000001</v>
       </c>
       <c r="M18" s="57">
         <f t="shared" si="6"/>
-        <v>206389.92000099999</v>
-      </c>
-      <c r="N18" s="170"/>
-      <c r="O18" s="138">
+        <v>175853.35972777999</v>
+      </c>
+      <c r="N18" s="167"/>
+      <c r="O18" s="136">
         <f t="shared" si="7"/>
-        <v>143253.28195869998</v>
-      </c>
-      <c r="P18" s="169"/>
-      <c r="Q18" s="166"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>123519.38595499998</v>
+      </c>
+      <c r="P18" s="166"/>
+      <c r="Q18" s="163"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="161"/>
+      <c r="B19" s="158"/>
       <c r="C19" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="160">
+      <c r="D19" s="157">
         <v>7.4</v>
       </c>
       <c r="E19" s="126">
         <v>294818.42106860003</v>
       </c>
-      <c r="F19" s="175">
+      <c r="F19" s="172">
         <f t="shared" si="10"/>
         <v>294818.42106860003</v>
       </c>
-      <c r="G19" s="182">
+      <c r="G19" s="179">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3259,11 +3262,11 @@
       </c>
       <c r="I19" s="64">
         <f t="shared" si="3"/>
-        <v>166469.15287799999</v>
+        <v>98922.241699999999</v>
       </c>
       <c r="J19" s="56">
         <f>Edesur!N26</f>
-        <v>89675.839061999985</v>
+        <v>77235.70629320007</v>
       </c>
       <c r="K19" s="64">
         <f t="shared" si="4"/>
@@ -3271,46 +3274,46 @@
       </c>
       <c r="L19" s="64">
         <f t="shared" si="5"/>
-        <v>37000</v>
+        <v>76517.96100000001</v>
       </c>
       <c r="M19" s="57">
         <f t="shared" si="6"/>
-        <v>293144.99193999998</v>
-      </c>
-      <c r="O19" s="138">
+        <v>252675.90899320011</v>
+      </c>
+      <c r="O19" s="136">
         <f t="shared" si="7"/>
-        <v>203469.15287799999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>175440.20270000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="191"/>
+      <c r="B20" s="186"/>
       <c r="C20" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="160">
+      <c r="D20" s="157">
         <v>1.08</v>
       </c>
       <c r="E20" s="126">
         <v>435982.31791082409</v>
       </c>
-      <c r="F20" s="175">
-        <v>0</v>
-      </c>
-      <c r="G20" s="182">
+      <c r="F20" s="172">
+        <v>0</v>
+      </c>
+      <c r="G20" s="179">
         <f t="shared" si="1"/>
         <v>435982.31791082409</v>
       </c>
       <c r="H20" s="64"/>
       <c r="I20" s="64">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J20" s="64">
         <f>Edesur!N27</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K20" s="64">
         <f t="shared" si="4"/>
@@ -3318,18 +3321,18 @@
       </c>
       <c r="L20" s="64">
         <f t="shared" si="5"/>
-        <v>5400</v>
-      </c>
-      <c r="M20" s="174">
+        <v>11167.486200000001</v>
+      </c>
+      <c r="M20" s="171">
         <f t="shared" si="6"/>
-        <v>478765.64105882408</v>
-      </c>
-      <c r="O20" s="138">
+        <v>471152.46976226405</v>
+      </c>
+      <c r="O20" s="136">
         <f t="shared" si="7"/>
-        <v>465677.81589842407</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>461587.10425082408</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3343,11 +3346,11 @@
       <c r="E21" s="126">
         <v>36601.116018119996</v>
       </c>
-      <c r="F21" s="175">
+      <c r="F21" s="172">
         <f t="shared" si="10"/>
         <v>36601.116018119996</v>
       </c>
-      <c r="G21" s="181">
+      <c r="G21" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3357,11 +3360,11 @@
       </c>
       <c r="I21" s="56">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J21" s="56">
         <f>Edesur!N28</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K21" s="56">
         <f t="shared" si="4"/>
@@ -3369,37 +3372,38 @@
       </c>
       <c r="L21" s="56">
         <f t="shared" si="5"/>
-        <v>5400</v>
+        <v>11167.486200000001</v>
       </c>
       <c r="M21" s="57">
         <f t="shared" si="6"/>
-        <v>42783.323148000003</v>
-      </c>
-      <c r="O21" s="138">
+        <v>35170.151851440001</v>
+      </c>
+      <c r="O21" s="136">
         <f t="shared" si="7"/>
-        <v>29695.4979876</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <v>25604.786339999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="161"/>
+      <c r="B22" s="158"/>
       <c r="C22" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="160">
+      <c r="D22" s="157">
         <v>1.08</v>
       </c>
       <c r="E22" s="126">
         <v>36601.116018119996</v>
       </c>
-      <c r="F22" s="175">
-        <v>47141.650748520005</v>
-      </c>
-      <c r="G22" s="182">
+      <c r="F22" s="172">
+        <f>E22</f>
+        <v>36601.116018119996</v>
+      </c>
+      <c r="G22" s="179">
         <f t="shared" si="1"/>
-        <v>-10540.53473040001</v>
+        <v>0</v>
       </c>
       <c r="H22" s="64">
         <f t="shared" si="2"/>
@@ -3407,11 +3411,11 @@
       </c>
       <c r="I22" s="64">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J22" s="64">
         <f>Edesur!N29</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K22" s="64">
         <f t="shared" si="4"/>
@@ -3419,18 +3423,18 @@
       </c>
       <c r="L22" s="64">
         <f t="shared" si="5"/>
-        <v>5400</v>
-      </c>
-      <c r="M22" s="174">
+        <v>11167.486200000001</v>
+      </c>
+      <c r="M22" s="171">
         <f t="shared" si="6"/>
-        <v>32242.788417599993</v>
-      </c>
-      <c r="O22" s="138">
+        <v>35170.151851440001</v>
+      </c>
+      <c r="O22" s="136">
         <f t="shared" si="7"/>
-        <v>19154.96325719999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <v>25604.786339999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3444,25 +3448,22 @@
       <c r="E23" s="126">
         <v>36601.116018119996</v>
       </c>
-      <c r="F23" s="175">
-        <f>E23</f>
+      <c r="F23" s="172"/>
+      <c r="G23" s="178">
+        <f t="shared" si="1"/>
         <v>36601.116018119996</v>
-      </c>
-      <c r="G23" s="181">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="H23" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1464.0446407247998</v>
       </c>
       <c r="I23" s="56">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J23" s="56">
         <f>Edesur!N30</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K23" s="56">
         <f t="shared" si="4"/>
@@ -3470,18 +3471,18 @@
       </c>
       <c r="L23" s="56">
         <f t="shared" si="5"/>
-        <v>5400</v>
+        <v>11167.486200000001</v>
       </c>
       <c r="M23" s="57">
         <f t="shared" si="6"/>
-        <v>42783.323148000003</v>
-      </c>
-      <c r="O23" s="138">
+        <v>73235.312510284799</v>
+      </c>
+      <c r="O23" s="136">
         <f t="shared" si="7"/>
-        <v>29695.4979876</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>63669.946998844796</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3497,11 +3498,11 @@
       <c r="E24" s="126">
         <v>36601.116018119996</v>
       </c>
-      <c r="F24" s="175">
+      <c r="F24" s="172">
         <f t="shared" ref="F24" si="11">E24</f>
         <v>36601.116018119996</v>
       </c>
-      <c r="G24" s="181">
+      <c r="G24" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3511,11 +3512,11 @@
       </c>
       <c r="I24" s="56">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J24" s="56">
         <f>Edesur!N31</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K24" s="56">
         <f t="shared" si="4"/>
@@ -3523,22 +3524,22 @@
       </c>
       <c r="L24" s="56">
         <f t="shared" si="5"/>
-        <v>5400</v>
+        <v>11167.486200000001</v>
       </c>
       <c r="M24" s="57">
         <f t="shared" si="6"/>
-        <v>42783.323148000003</v>
-      </c>
-      <c r="O24" s="138">
+        <v>35170.151851440001</v>
+      </c>
+      <c r="O24" s="136">
         <f t="shared" si="7"/>
-        <v>29695.4979876</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+        <v>25604.786339999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="161" t="s">
+      <c r="B25" s="158" t="s">
         <v>103</v>
       </c>
       <c r="C25" s="60" t="s">
@@ -3550,25 +3551,22 @@
       <c r="E25" s="126">
         <v>36601.116018119996</v>
       </c>
-      <c r="F25" s="175">
-        <f>E25</f>
+      <c r="F25" s="172"/>
+      <c r="G25" s="178">
+        <f t="shared" si="1"/>
         <v>36601.116018119996</v>
-      </c>
-      <c r="G25" s="181">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="H25" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1464.0446407247998</v>
       </c>
       <c r="I25" s="56">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J25" s="56">
         <f>Edesur!N32</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K25" s="56">
         <f t="shared" si="4"/>
@@ -3576,18 +3574,18 @@
       </c>
       <c r="L25" s="56">
         <f t="shared" si="5"/>
-        <v>5400</v>
+        <v>11167.486200000001</v>
       </c>
       <c r="M25" s="57">
         <f t="shared" si="6"/>
-        <v>42783.323148000003</v>
-      </c>
-      <c r="O25" s="138">
+        <v>73235.312510284799</v>
+      </c>
+      <c r="O25" s="136">
         <f t="shared" si="7"/>
-        <v>29695.4979876</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <v>63669.946998844796</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3601,11 +3599,11 @@
       <c r="E26" s="126">
         <v>36601.116018119996</v>
       </c>
-      <c r="F26" s="175">
+      <c r="F26" s="172">
         <f t="shared" ref="F26:F28" si="12">E26</f>
         <v>36601.116018119996</v>
       </c>
-      <c r="G26" s="181">
+      <c r="G26" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3615,11 +3613,11 @@
       </c>
       <c r="I26" s="56">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J26" s="56">
         <f>Edesur!N33</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K26" s="56">
         <f t="shared" si="4"/>
@@ -3627,18 +3625,18 @@
       </c>
       <c r="L26" s="56">
         <f t="shared" si="5"/>
-        <v>5400</v>
+        <v>11167.486200000001</v>
       </c>
       <c r="M26" s="57">
         <f t="shared" si="6"/>
-        <v>42783.323148000003</v>
-      </c>
-      <c r="O26" s="138">
+        <v>35170.151851440001</v>
+      </c>
+      <c r="O26" s="136">
         <f t="shared" si="7"/>
-        <v>29695.4979876</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+        <v>25604.786339999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3652,11 +3650,11 @@
       <c r="E27" s="126">
         <v>36601.116018119996</v>
       </c>
-      <c r="F27" s="175">
+      <c r="F27" s="172">
         <f t="shared" si="12"/>
         <v>36601.116018119996</v>
       </c>
-      <c r="G27" s="181">
+      <c r="G27" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3666,11 +3664,11 @@
       </c>
       <c r="I27" s="56">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J27" s="56">
         <f>Edesur!N34</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K27" s="56">
         <f t="shared" si="4"/>
@@ -3678,22 +3676,22 @@
       </c>
       <c r="L27" s="56">
         <f t="shared" si="5"/>
-        <v>5400</v>
+        <v>11167.486200000001</v>
       </c>
       <c r="M27" s="57">
         <f t="shared" si="6"/>
-        <v>42783.323148000003</v>
-      </c>
-      <c r="O27" s="138">
+        <v>35170.151851440001</v>
+      </c>
+      <c r="O27" s="136">
         <f t="shared" si="7"/>
-        <v>29695.4979876</v>
+        <v>25604.786339999999</v>
       </c>
       <c r="P27" s="44">
         <f>F27+F26+F19</f>
         <v>368020.65310484002</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3708,11 +3706,11 @@
       <c r="E28" s="126">
         <v>36601.116018119996</v>
       </c>
-      <c r="F28" s="175">
+      <c r="F28" s="172">
         <f t="shared" si="12"/>
         <v>36601.116018119996</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3722,11 +3720,11 @@
       </c>
       <c r="I28" s="56">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J28" s="56">
         <f>Edesur!N35</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" si="4"/>
@@ -3734,18 +3732,18 @@
       </c>
       <c r="L28" s="56">
         <f t="shared" si="5"/>
-        <v>5400</v>
+        <v>11167.486200000001</v>
       </c>
       <c r="M28" s="57">
         <f t="shared" si="6"/>
-        <v>42783.323148000003</v>
-      </c>
-      <c r="O28" s="138">
+        <v>35170.151851440001</v>
+      </c>
+      <c r="O28" s="136">
         <f t="shared" si="7"/>
-        <v>29695.4979876</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+        <v>25604.786339999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3761,22 +3759,25 @@
       <c r="E29" s="126">
         <v>85628.43279658079</v>
       </c>
-      <c r="F29" s="175"/>
-      <c r="G29" s="181">
+      <c r="F29" s="172">
+        <f>E29</f>
+        <v>85628.43279658079</v>
+      </c>
+      <c r="G29" s="178">
         <f t="shared" si="1"/>
-        <v>85628.43279658079</v>
+        <v>0</v>
       </c>
       <c r="H29" s="56">
         <f t="shared" si="2"/>
-        <v>3425.1373118632318</v>
+        <v>0</v>
       </c>
       <c r="I29" s="56">
         <f t="shared" si="3"/>
-        <v>24295.4979876</v>
+        <v>14437.300139999999</v>
       </c>
       <c r="J29" s="56">
         <f>Edesur!N36</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="K29" s="56">
         <f t="shared" si="4"/>
@@ -3784,18 +3785,18 @@
       </c>
       <c r="L29" s="56">
         <f t="shared" si="5"/>
-        <v>5400</v>
+        <v>11167.486200000001</v>
       </c>
       <c r="M29" s="57">
         <f t="shared" si="6"/>
-        <v>131836.89325644402</v>
-      </c>
-      <c r="O29" s="138">
+        <v>35170.151851440001</v>
+      </c>
+      <c r="O29" s="136">
         <f t="shared" si="7"/>
-        <v>118749.06809604402</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>25604.786339999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3810,7 +3811,7 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3823,13 +3824,13 @@
       <c r="E31" s="73"/>
       <c r="F31" s="132">
         <f>SUM(F3:F30)</f>
-        <v>3584406.0490640621</v>
+        <v>3661916.314806771</v>
       </c>
       <c r="G31" s="75"/>
       <c r="H31" s="75"/>
       <c r="I31" s="133">
         <f>SUM(I3:I30)</f>
-        <v>2249583.1469999999</v>
+        <v>1336787.0499999993</v>
       </c>
       <c r="J31" s="133"/>
       <c r="K31" s="133">
@@ -3839,16 +3840,16 @@
       <c r="L31" s="132"/>
       <c r="M31" s="132">
         <f>SUM(M3:M29)</f>
-        <v>4887467.1258234903</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4415121.5128804985</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K32" s="22"/>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F34" s="44"/>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E36" s="21"/>
     </row>
   </sheetData>
@@ -3867,163 +3868,163 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="0.140625" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+    <col min="5" max="5" width="5.21875" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="5.109375" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="207" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="208"/>
-      <c r="J1" s="208"/>
-      <c r="K1" s="208"/>
-      <c r="L1" s="208"/>
-      <c r="M1" s="208"/>
-      <c r="N1" s="209"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="203"/>
+      <c r="M1" s="203"/>
+      <c r="N1" s="204"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="146"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="143"/>
+      <c r="M2" s="143"/>
+      <c r="N2" s="143"/>
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="146"/>
-      <c r="J3" s="146"/>
-      <c r="K3" s="146"/>
-      <c r="L3" s="146"/>
-      <c r="M3" s="146"/>
-      <c r="N3" s="146"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
-      <c r="C4" s="148"/>
-      <c r="D4" s="148"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="148"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="146" t="s">
+      <c r="C4" s="145"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="143" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="146"/>
-      <c r="N4" s="146"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="143"/>
+      <c r="N4" s="143"/>
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
-      <c r="C5" s="148"/>
-      <c r="D5" s="148"/>
-      <c r="E5" s="148"/>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="146"/>
-      <c r="J5" s="146"/>
-      <c r="K5" s="146"/>
-      <c r="L5" s="146"/>
-      <c r="M5" s="146"/>
-      <c r="N5" s="146"/>
+      <c r="C5" s="145"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="143"/>
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
-      <c r="C6" s="172" t="str">
+      <c r="C6" s="169" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 17/04</v>
       </c>
       <c r="D6" s="28"/>
-      <c r="E6" s="146"/>
-      <c r="F6" s="146"/>
-      <c r="G6" s="146"/>
-      <c r="H6" s="147"/>
-      <c r="I6" s="146"/>
-      <c r="J6" s="146"/>
-      <c r="K6" s="146"/>
-      <c r="L6" s="146"/>
-      <c r="M6" s="146"/>
-      <c r="N6" s="146"/>
+      <c r="E6" s="143"/>
+      <c r="F6" s="143"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="144"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
+      <c r="L6" s="143"/>
+      <c r="M6" s="143"/>
+      <c r="N6" s="143"/>
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="180">
-        <f>-'detalle y gastos'!C49</f>
+      <c r="C7" s="177">
+        <f>-'detalle y gastos'!C50</f>
         <v>1024355.45</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="146"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="146"/>
-      <c r="J7" s="146"/>
-      <c r="K7" s="146"/>
-      <c r="L7" s="146"/>
-      <c r="M7" s="146"/>
-      <c r="N7" s="146"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="143"/>
+      <c r="L7" s="143"/>
+      <c r="M7" s="143"/>
+      <c r="N7" s="143"/>
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -4035,20 +4036,20 @@
       <c r="H8" s="83"/>
       <c r="I8" s="82"/>
       <c r="J8" s="78"/>
-      <c r="K8" s="179">
+      <c r="K8" s="176">
         <f>C8-J38</f>
-        <v>187480.21300000005</v>
-      </c>
-      <c r="L8" s="211">
+        <v>-138673.45820000005</v>
+      </c>
+      <c r="L8" s="206">
         <f>C7-J38</f>
-        <v>1211835.6629999999</v>
-      </c>
-      <c r="M8" s="211"/>
+        <v>885681.99179999996</v>
+      </c>
+      <c r="M8" s="206"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="86" t="s">
         <v>78</v>
       </c>
@@ -4079,10 +4080,10 @@
       <c r="J9" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="183" t="s">
+      <c r="K9" s="180" t="s">
         <v>84</v>
       </c>
-      <c r="L9" s="183" t="s">
+      <c r="L9" s="180" t="s">
         <v>84</v>
       </c>
       <c r="M9" s="122" t="s">
@@ -4093,7 +4094,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="97">
         <v>1</v>
       </c>
@@ -4129,11 +4130,11 @@
       </c>
       <c r="K10" s="114">
         <f>K8*E10%</f>
-        <v>9580.2388843000044</v>
-      </c>
-      <c r="L10" s="186">
+        <v>-7086.2137140200039</v>
+      </c>
+      <c r="L10" s="183">
         <f>L$8*E10/S$12</f>
-        <v>61924.802379299996</v>
+        <v>45258.349780980003</v>
       </c>
       <c r="M10" s="105">
         <f>G10-F10</f>
@@ -4141,15 +4142,15 @@
       </c>
       <c r="N10" s="103">
         <f>J10+L10</f>
-        <v>70956.490479300017</v>
+        <v>54290.037880980017</v>
       </c>
       <c r="O10" s="96">
         <f>N10+'prorrateo '!M3</f>
-        <v>282416.67977030005</v>
+        <v>229728.64816695999</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="98">
         <v>2</v>
       </c>
@@ -4185,11 +4186,11 @@
       </c>
       <c r="K11" s="114">
         <f>K8*E11%</f>
-        <v>9542.7428417000028</v>
-      </c>
-      <c r="L11" s="186">
+        <v>-7058.4790223800028</v>
+      </c>
+      <c r="L11" s="183">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>61682.435246699992</v>
+        <v>45081.213382620001</v>
       </c>
       <c r="M11" s="105">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
@@ -4197,15 +4198,15 @@
       </c>
       <c r="N11" s="103">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>61860.630546699955</v>
+        <v>45259.408682619964</v>
       </c>
       <c r="O11" s="96">
         <f>N11+'prorrateo '!M4</f>
-        <v>466237.7531637823</v>
+        <v>528648.89694832219</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="97">
         <v>3</v>
       </c>
@@ -4241,11 +4242,11 @@
       </c>
       <c r="K12" s="114">
         <f>K8*E12%</f>
-        <v>9449.0027352000016</v>
-      </c>
-      <c r="L12" s="186">
+        <v>-6989.1422932800024</v>
+      </c>
+      <c r="L12" s="183">
         <f t="shared" si="3"/>
-        <v>61076.517415199996</v>
+        <v>44638.372386719995</v>
       </c>
       <c r="M12" s="105">
         <f>G12-F12</f>
@@ -4253,31 +4254,31 @@
       </c>
       <c r="N12" s="103">
         <f t="shared" si="5"/>
-        <v>70267.6434152</v>
+        <v>53829.498386719992</v>
       </c>
       <c r="O12" s="96">
         <f>N12+'prorrateo '!M5</f>
-        <v>218118.46220808869</v>
+        <v>190546.87844420868</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="97">
         <v>4</v>
       </c>
       <c r="B13" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="149" t="s">
+      <c r="C13" s="146" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="150">
+      <c r="E13" s="147">
         <v>5.21</v>
       </c>
       <c r="F13" s="102">
@@ -4290,7 +4291,7 @@
         <f t="shared" si="1"/>
         <v>57.700000000000045</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="148">
         <f t="shared" si="0"/>
         <v>4.0390000000000033</v>
       </c>
@@ -4298,29 +4299,29 @@
         <f t="shared" si="2"/>
         <v>5411.5099000000046</v>
       </c>
-      <c r="K13" s="187">
+      <c r="K13" s="184">
         <f>K8*E13%</f>
-        <v>9767.7190973000033</v>
-      </c>
-      <c r="L13" s="186">
+        <v>-7224.8871722200029</v>
+      </c>
+      <c r="L13" s="183">
         <f t="shared" si="3"/>
-        <v>63136.638042300001</v>
-      </c>
-      <c r="M13" s="152">
+        <v>46144.031772779999</v>
+      </c>
+      <c r="M13" s="149">
         <f t="shared" si="4"/>
         <v>57.700000000000045</v>
       </c>
       <c r="N13" s="103">
         <f t="shared" si="5"/>
-        <v>68548.147942300013</v>
+        <v>51555.541672780004</v>
       </c>
       <c r="O13" s="96">
         <f>N13+'prorrateo '!M6</f>
-        <v>280349.57784330001</v>
+        <v>226630.46930056001</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="97">
         <v>6</v>
       </c>
@@ -4356,11 +4357,11 @@
       </c>
       <c r="K14" s="114">
         <f>K8*E14%</f>
-        <v>9580.2388843000044</v>
-      </c>
-      <c r="L14" s="186">
+        <v>-7086.2137140200039</v>
+      </c>
+      <c r="L14" s="183">
         <f t="shared" si="3"/>
-        <v>61924.802379299996</v>
+        <v>45258.349780980003</v>
       </c>
       <c r="M14" s="105">
         <f t="shared" si="4"/>
@@ -4368,15 +4369,15 @@
       </c>
       <c r="N14" s="103">
         <f t="shared" si="5"/>
-        <v>73516.875579300031</v>
+        <v>56850.422980980038</v>
       </c>
       <c r="O14" s="96">
         <f>N14+'prorrateo '!M7</f>
-        <v>231251.19718720013</v>
+        <v>234849.4155838601</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="97">
         <v>7</v>
       </c>
@@ -4412,11 +4413,11 @@
       </c>
       <c r="K15" s="114">
         <f>K8*E15%</f>
-        <v>9542.7428417000028</v>
-      </c>
-      <c r="L15" s="186">
+        <v>-7058.4790223800028</v>
+      </c>
+      <c r="L15" s="183">
         <f t="shared" si="3"/>
-        <v>61682.435246699992</v>
+        <v>45081.213382620001</v>
       </c>
       <c r="M15" s="105">
         <f t="shared" si="4"/>
@@ -4424,14 +4425,14 @@
       </c>
       <c r="N15" s="103">
         <f t="shared" si="5"/>
-        <v>69204.152646699979</v>
+        <v>52602.93078261998</v>
       </c>
       <c r="O15" s="96">
         <f>N15+'prorrateo '!M8</f>
-        <v>278362.08747569995</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <v>225880.27126023994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="97">
         <v>8</v>
       </c>
@@ -4467,11 +4468,11 @@
       </c>
       <c r="K16" s="114">
         <f>K8*E16%</f>
-        <v>9580.2388843000044</v>
-      </c>
-      <c r="L16" s="186">
+        <v>-7086.2137140200039</v>
+      </c>
+      <c r="L16" s="183">
         <f t="shared" si="3"/>
-        <v>61924.802379299996</v>
+        <v>45258.349780980003</v>
       </c>
       <c r="M16" s="105">
         <f t="shared" si="4"/>
@@ -4479,14 +4480,14 @@
       </c>
       <c r="N16" s="103">
         <f t="shared" si="5"/>
-        <v>69615.336379300003</v>
+        <v>52948.883780980002</v>
       </c>
       <c r="O16" s="96">
         <f>N16+'prorrateo '!M9</f>
-        <v>279734.37157030002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>227046.33996696002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="97">
         <v>9</v>
       </c>
@@ -4522,11 +4523,11 @@
       </c>
       <c r="K17" s="114">
         <f>K8*E17%</f>
-        <v>9542.7428417000028</v>
-      </c>
-      <c r="L17" s="186">
+        <v>-7058.4790223800028</v>
+      </c>
+      <c r="L17" s="183">
         <f t="shared" si="3"/>
-        <v>61682.435246699992</v>
+        <v>45081.213382620001</v>
       </c>
       <c r="M17" s="105">
         <f t="shared" si="4"/>
@@ -4534,14 +4535,14 @@
       </c>
       <c r="N17" s="103">
         <f t="shared" si="5"/>
-        <v>63164.269846700008</v>
+        <v>46563.047982620017</v>
       </c>
       <c r="O17" s="96">
         <f>N17+'prorrateo '!M10</f>
-        <v>217748.98115996009</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>213800.31021410006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="97">
         <v>10</v>
       </c>
@@ -4577,11 +4578,11 @@
       </c>
       <c r="K18" s="114">
         <f>K8*E18%</f>
-        <v>9449.0027352000016</v>
-      </c>
-      <c r="L18" s="186">
+        <v>-6989.1422932800024</v>
+      </c>
+      <c r="L18" s="183">
         <f t="shared" si="3"/>
-        <v>61076.517415199996</v>
+        <v>44638.372386719995</v>
       </c>
       <c r="M18" s="105">
         <f t="shared" si="4"/>
@@ -4589,14 +4590,14 @@
       </c>
       <c r="N18" s="103">
         <f t="shared" si="5"/>
-        <v>66778.767015199977</v>
+        <v>50340.621986719969</v>
       </c>
       <c r="O18" s="96">
         <f>N18+'prorrateo '!M11</f>
-        <v>272136.52463919995</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>220170.24689343991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="97">
         <v>11</v>
       </c>
@@ -4632,11 +4633,11 @@
       </c>
       <c r="K19" s="114">
         <f>K8*E19%</f>
-        <v>9767.7190973000033</v>
-      </c>
-      <c r="L19" s="186">
+        <v>-7224.8871722200029</v>
+      </c>
+      <c r="L19" s="183">
         <f t="shared" si="3"/>
-        <v>63136.638042300001</v>
+        <v>46144.031772779999</v>
       </c>
       <c r="M19" s="105">
         <f>G19-F19</f>
@@ -4644,14 +4645,14 @@
       </c>
       <c r="N19" s="103">
         <f t="shared" si="5"/>
-        <v>79933.889742300031</v>
+        <v>62941.283472780036</v>
       </c>
       <c r="O19" s="96">
         <f>N19+'prorrateo '!M12</f>
-        <v>303121.06144330004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>249401.95290056005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="97">
         <v>12</v>
       </c>
@@ -4687,11 +4688,11 @@
       </c>
       <c r="K20" s="114">
         <f>K8*E20%</f>
-        <v>9580.2388843000044</v>
-      </c>
-      <c r="L20" s="186">
+        <v>-7086.2137140200039</v>
+      </c>
+      <c r="L20" s="183">
         <f t="shared" si="3"/>
-        <v>61924.802379299996</v>
+        <v>45258.349780980003</v>
       </c>
       <c r="M20" s="105">
         <f t="shared" si="4"/>
@@ -4699,14 +4700,14 @@
       </c>
       <c r="N20" s="103">
         <f t="shared" si="5"/>
-        <v>76808.799279299972</v>
+        <v>60142.346680979987</v>
       </c>
       <c r="O20" s="96">
         <f>N20+'prorrateo '!M13</f>
-        <v>235068.34406149967</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>241433.36632580764</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="97">
         <v>13</v>
       </c>
@@ -4742,11 +4743,11 @@
       </c>
       <c r="K21" s="114">
         <f>K8*E21%</f>
-        <v>9542.7428417000028</v>
-      </c>
-      <c r="L21" s="186">
+        <v>-7058.4790223800028</v>
+      </c>
+      <c r="L21" s="183">
         <f t="shared" si="3"/>
-        <v>61682.435246699992</v>
+        <v>45081.213382620001</v>
       </c>
       <c r="M21" s="105">
         <f t="shared" si="4"/>
@@ -4754,14 +4755,14 @@
       </c>
       <c r="N21" s="103">
         <f t="shared" si="5"/>
-        <v>66728.175846700004</v>
+        <v>50126.95398262002</v>
       </c>
       <c r="O21" s="96">
         <f>N21+'prorrateo '!M14</f>
-        <v>215208.79190211699</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>408911.39814886893</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="97">
         <v>14</v>
       </c>
@@ -4780,41 +4781,43 @@
       <c r="F22" s="102">
         <v>3145.8</v>
       </c>
-      <c r="G22" s="196"/>
+      <c r="G22" s="102">
+        <v>3264.9</v>
+      </c>
       <c r="H22" s="103">
         <f t="shared" si="1"/>
-        <v>-3145.8</v>
+        <v>119.09999999999991</v>
       </c>
       <c r="I22" s="104">
         <f t="shared" si="0"/>
-        <v>-220.20600000000005</v>
+        <v>8.3369999999999944</v>
       </c>
       <c r="J22" s="114">
         <f t="shared" si="2"/>
-        <v>-295035.14460000006</v>
+        <v>11170.031699999992</v>
       </c>
       <c r="K22" s="114">
         <f>K8*E22%</f>
-        <v>9449.0027352000016</v>
-      </c>
-      <c r="L22" s="186">
+        <v>-6989.1422932800024</v>
+      </c>
+      <c r="L22" s="183">
         <f t="shared" si="3"/>
-        <v>61076.517415199996</v>
+        <v>44638.372386719995</v>
       </c>
       <c r="M22" s="105">
         <f t="shared" si="4"/>
-        <v>-3145.8</v>
+        <v>119.09999999999991</v>
       </c>
       <c r="N22" s="103">
         <f t="shared" si="5"/>
-        <v>-233958.62718480005</v>
+        <v>55808.404086719987</v>
       </c>
       <c r="O22" s="96">
         <f>N22+'prorrateo '!M15</f>
-        <v>130270.81977837184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>270168.46474105585</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="97">
         <v>15</v>
       </c>
@@ -4850,11 +4853,11 @@
       </c>
       <c r="K23" s="114">
         <f>K8*E23%</f>
-        <v>9767.7190973000033</v>
-      </c>
-      <c r="L23" s="186">
+        <v>-7224.8871722200029</v>
+      </c>
+      <c r="L23" s="183">
         <f t="shared" si="3"/>
-        <v>63136.638042300001</v>
+        <v>46144.031772779999</v>
       </c>
       <c r="M23" s="105">
         <f t="shared" si="4"/>
@@ -4862,14 +4865,14 @@
       </c>
       <c r="N23" s="103">
         <f t="shared" si="5"/>
-        <v>76163.65234229996</v>
+        <v>59171.046072779965</v>
       </c>
       <c r="O23" s="96">
         <f>N23+'prorrateo '!M16</f>
-        <v>228395.70519058354</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>241801.16664784355</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="97">
         <v>16</v>
       </c>
@@ -4889,42 +4892,42 @@
         <v>2020.8</v>
       </c>
       <c r="G24" s="102">
-        <v>2020.8</v>
+        <v>2042.8</v>
       </c>
       <c r="H24" s="103">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I24" s="104">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="J24" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2063.3140000000003</v>
       </c>
       <c r="K24" s="114">
         <f>K8*E24%</f>
-        <v>9449.0027352000016</v>
-      </c>
-      <c r="L24" s="186">
+        <v>-6989.1422932800024</v>
+      </c>
+      <c r="L24" s="183">
         <f t="shared" si="3"/>
-        <v>61076.517415199996</v>
+        <v>44638.372386719995</v>
       </c>
       <c r="M24" s="105">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N24" s="103">
         <f t="shared" si="5"/>
-        <v>61076.517415199996</v>
+        <v>46701.686386719994</v>
       </c>
       <c r="O24" s="96">
         <f>N24+'prorrateo '!M17</f>
-        <v>547847.99301161873</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>212892.37569343997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="97">
         <v>17</v>
       </c>
@@ -4944,42 +4947,42 @@
         <v>2317.3000000000002</v>
       </c>
       <c r="G25" s="102">
-        <v>2317.3000000000002</v>
+        <v>2383.3000000000002</v>
       </c>
       <c r="H25" s="103">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I25" s="104">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="J25" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6189.942</v>
       </c>
       <c r="K25" s="114">
         <f>K8*E25%</f>
-        <v>9767.7190973000033</v>
-      </c>
-      <c r="L25" s="186">
+        <v>-7224.8871722200029</v>
+      </c>
+      <c r="L25" s="183">
         <f t="shared" si="3"/>
-        <v>63136.638042300001</v>
+        <v>46144.031772779999</v>
       </c>
       <c r="M25" s="105">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="N25" s="103">
         <f t="shared" si="5"/>
-        <v>63136.638042300001</v>
+        <v>52333.973772780002</v>
       </c>
       <c r="O25" s="96">
         <f>N25+'prorrateo '!M18</f>
-        <v>269526.5580433</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>228187.33350055999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="97">
         <v>18</v>
       </c>
@@ -4999,89 +5002,89 @@
         <v>10444</v>
       </c>
       <c r="G26" s="102">
-        <v>10444</v>
+        <v>10568.7</v>
       </c>
       <c r="H26" s="103">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>124.70000000000073</v>
       </c>
       <c r="I26" s="104">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.7290000000000525</v>
       </c>
       <c r="J26" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11695.238900000069</v>
       </c>
       <c r="K26" s="114">
         <f>K8*E26%</f>
-        <v>13873.535762000005</v>
-      </c>
-      <c r="L26" s="186">
+        <v>-10261.835906800005</v>
+      </c>
+      <c r="L26" s="183">
         <f t="shared" si="3"/>
-        <v>89675.839061999985</v>
+        <v>65540.467393200001</v>
       </c>
       <c r="M26" s="105">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>124.70000000000073</v>
       </c>
       <c r="N26" s="103">
         <f>J26+L26</f>
-        <v>89675.839061999985</v>
+        <v>77235.70629320007</v>
       </c>
       <c r="O26" s="96">
         <f>N26+'prorrateo '!M19</f>
-        <v>382820.83100199996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="192">
+        <v>329911.61528640019</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="187">
         <v>19</v>
       </c>
-      <c r="B27" s="193">
+      <c r="B27" s="188">
         <v>19</v>
       </c>
-      <c r="C27" s="145" t="s">
+      <c r="C27" s="150" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="194"/>
-      <c r="E27" s="195">
+      <c r="D27" s="191"/>
+      <c r="E27" s="192">
         <v>1.08</v>
       </c>
-      <c r="F27" s="196"/>
-      <c r="G27" s="196"/>
-      <c r="H27" s="136">
+      <c r="F27" s="102"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="103">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="197">
+      <c r="I27" s="104">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="188"/>
-      <c r="K27" s="188"/>
-      <c r="L27" s="189">
+      <c r="J27" s="114"/>
+      <c r="K27" s="114"/>
+      <c r="L27" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
-      </c>
-      <c r="M27" s="137">
-        <v>0</v>
-      </c>
-      <c r="N27" s="136">
+        <v>9565.3655114400008</v>
+      </c>
+      <c r="M27" s="105">
+        <v>0</v>
+      </c>
+      <c r="N27" s="103">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O27" s="96">
         <f>N27+'prorrateo '!M20</f>
-        <v>491853.46621922409</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>480717.83527370403</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="97">
         <v>20</v>
       </c>
       <c r="B28" s="89"/>
-      <c r="C28" s="153" t="s">
+      <c r="C28" s="150" t="s">
         <v>66</v>
       </c>
       <c r="D28" s="101"/>
@@ -5093,32 +5096,32 @@
       <c r="H28" s="103">
         <v>0</v>
       </c>
-      <c r="I28" s="154">
+      <c r="I28" s="151">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="155"/>
+      <c r="J28" s="152"/>
       <c r="K28" s="114"/>
-      <c r="L28" s="186">
+      <c r="L28" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="M28" s="105">
         <v>0</v>
       </c>
       <c r="N28" s="103">
         <f t="shared" si="6"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O28" s="96">
         <f>N28+'prorrateo '!M21</f>
-        <v>55871.148308400006</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <v>44735.517362880004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="97"/>
       <c r="B29" s="89"/>
-      <c r="C29" s="153" t="s">
+      <c r="C29" s="150" t="s">
         <v>67</v>
       </c>
       <c r="D29" s="101"/>
@@ -5128,29 +5131,29 @@
       <c r="F29" s="101"/>
       <c r="G29" s="101"/>
       <c r="H29" s="103"/>
-      <c r="I29" s="154"/>
-      <c r="J29" s="155"/>
+      <c r="I29" s="151"/>
+      <c r="J29" s="152"/>
       <c r="K29" s="114"/>
-      <c r="L29" s="186">
+      <c r="L29" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="M29" s="105">
         <v>0</v>
       </c>
       <c r="N29" s="103">
         <f t="shared" si="6"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O29" s="96">
         <f>N29+'prorrateo '!M22</f>
-        <v>45330.613577999997</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>44735.517362880004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="97"/>
       <c r="B30" s="89"/>
-      <c r="C30" s="153" t="s">
+      <c r="C30" s="150" t="s">
         <v>68</v>
       </c>
       <c r="D30" s="101"/>
@@ -5160,29 +5163,29 @@
       <c r="F30" s="101"/>
       <c r="G30" s="101"/>
       <c r="H30" s="103"/>
-      <c r="I30" s="154"/>
-      <c r="J30" s="155"/>
+      <c r="I30" s="151"/>
+      <c r="J30" s="152"/>
       <c r="K30" s="114"/>
-      <c r="L30" s="186">
+      <c r="L30" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="M30" s="105">
         <v>0</v>
       </c>
       <c r="N30" s="103">
         <f t="shared" si="6"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O30" s="96">
         <f>N30+'prorrateo '!M23</f>
-        <v>55871.148308400006</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>82800.678021724802</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="97"/>
       <c r="B31" s="89"/>
-      <c r="C31" s="153" t="s">
+      <c r="C31" s="150" t="s">
         <v>69</v>
       </c>
       <c r="D31" s="101" t="s">
@@ -5194,29 +5197,29 @@
       <c r="F31" s="101"/>
       <c r="G31" s="101"/>
       <c r="H31" s="103"/>
-      <c r="I31" s="154"/>
-      <c r="J31" s="155"/>
+      <c r="I31" s="151"/>
+      <c r="J31" s="152"/>
       <c r="K31" s="114"/>
-      <c r="L31" s="186">
+      <c r="L31" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="M31" s="105">
         <v>0</v>
       </c>
       <c r="N31" s="103">
         <f t="shared" si="6"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O31" s="96">
         <f>N31+'prorrateo '!M24</f>
-        <v>55871.148308400006</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <v>44735.517362880004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="98"/>
-      <c r="B32" s="171"/>
-      <c r="C32" s="153" t="s">
+      <c r="B32" s="168"/>
+      <c r="C32" s="150" t="s">
         <v>70</v>
       </c>
       <c r="D32" s="101" t="s">
@@ -5228,26 +5231,26 @@
       <c r="F32" s="101"/>
       <c r="G32" s="101"/>
       <c r="H32" s="103"/>
-      <c r="I32" s="154"/>
-      <c r="J32" s="155"/>
+      <c r="I32" s="151"/>
+      <c r="J32" s="152"/>
       <c r="K32" s="114"/>
-      <c r="L32" s="186">
+      <c r="L32" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="M32" s="105">
         <v>0</v>
       </c>
       <c r="N32" s="103">
         <f t="shared" si="6"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O32" s="96">
         <f>N32+'prorrateo '!M25</f>
-        <v>55871.148308400006</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>82800.678021724802</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="97"/>
       <c r="B33" s="89"/>
       <c r="C33" s="127" t="s">
@@ -5265,23 +5268,23 @@
       <c r="I33" s="109"/>
       <c r="J33" s="128"/>
       <c r="K33" s="115"/>
-      <c r="L33" s="186">
+      <c r="L33" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="M33" s="105">
         <v>0</v>
       </c>
       <c r="N33" s="103">
         <f t="shared" si="6"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O33" s="96">
         <f>N33+'prorrateo '!M26</f>
-        <v>55871.148308400006</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>44735.517362880004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="97"/>
       <c r="B34" s="89"/>
       <c r="C34" s="127" t="s">
@@ -5299,28 +5302,28 @@
       <c r="I34" s="109"/>
       <c r="J34" s="128"/>
       <c r="K34" s="115"/>
-      <c r="L34" s="186">
+      <c r="L34" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="M34" s="105">
         <v>0</v>
       </c>
       <c r="N34" s="103">
         <f t="shared" si="6"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O34" s="96">
         <f>N34+'prorrateo '!M27</f>
-        <v>55871.148308400006</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>44735.517362880004</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="97">
         <v>21</v>
       </c>
       <c r="B35" s="89"/>
-      <c r="C35" s="153" t="s">
+      <c r="C35" s="150" t="s">
         <v>73</v>
       </c>
       <c r="D35" s="101"/>
@@ -5332,34 +5335,34 @@
       <c r="H35" s="103">
         <v>0</v>
       </c>
-      <c r="I35" s="154">
+      <c r="I35" s="151">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="156"/>
+      <c r="J35" s="153"/>
       <c r="K35" s="114"/>
-      <c r="L35" s="186">
+      <c r="L35" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="M35" s="105">
         <v>0</v>
       </c>
       <c r="N35" s="103">
         <f t="shared" si="6"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O35" s="96">
         <f>N35+'prorrateo '!M28</f>
-        <v>55871.148308400006</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>44735.517362880004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="97">
         <v>22</v>
       </c>
       <c r="B36" s="89"/>
-      <c r="C36" s="153" t="s">
+      <c r="C36" s="150" t="s">
         <v>74</v>
       </c>
       <c r="D36" s="101" t="s">
@@ -5373,29 +5376,29 @@
       <c r="H36" s="103">
         <v>0</v>
       </c>
-      <c r="I36" s="154">
+      <c r="I36" s="151">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="156"/>
+      <c r="J36" s="153"/>
       <c r="K36" s="114"/>
-      <c r="L36" s="186">
+      <c r="L36" s="183">
         <f t="shared" si="3"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="M36" s="105">
         <v>0</v>
       </c>
       <c r="N36" s="103">
         <f t="shared" si="6"/>
-        <v>13087.825160400002</v>
+        <v>9565.3655114400008</v>
       </c>
       <c r="O36" s="96">
         <f>N36+'prorrateo '!M29</f>
-        <v>144924.71841684403</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>44735.517362880004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="97">
         <v>23</v>
       </c>
@@ -5413,8 +5416,8 @@
         <v>0</v>
       </c>
       <c r="J37" s="129"/>
-      <c r="K37" s="184"/>
-      <c r="L37" s="185">
+      <c r="K37" s="181"/>
+      <c r="L37" s="182">
         <v>0</v>
       </c>
       <c r="M37" s="124">
@@ -5425,7 +5428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="97">
         <v>24</v>
       </c>
@@ -5439,21 +5442,21 @@
       <c r="I38" s="110"/>
       <c r="J38" s="115">
         <f>SUM(J10:J37)</f>
-        <v>-187480.21300000005</v>
+        <v>138673.45820000005</v>
       </c>
       <c r="K38" s="111"/>
       <c r="L38" s="111">
         <f>SUM(L10:L37)</f>
-        <v>1211835.6630000002</v>
+        <v>885681.99179999984</v>
       </c>
       <c r="M38" s="112"/>
       <c r="N38" s="108">
         <f>SUM(N10:N37)</f>
-        <v>1024355.4500000002</v>
+        <v>1024355.4499999997</v>
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="78"/>
       <c r="C39" s="90"/>
       <c r="D39" s="91"/>
@@ -5466,61 +5469,61 @@
       <c r="H39" s="92"/>
       <c r="I39" s="93">
         <f>SUM(I10:I38)</f>
-        <v>-139.93000000000004</v>
+        <v>103.50200000000005</v>
       </c>
       <c r="J39" s="123"/>
       <c r="K39" s="93"/>
       <c r="L39" s="130">
         <f>L38+J38</f>
-        <v>1024355.4500000002</v>
+        <v>1024355.45</v>
       </c>
       <c r="M39" s="92"/>
       <c r="N39" s="92"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="210"/>
-      <c r="D40" s="208"/>
-      <c r="E40" s="208"/>
-      <c r="F40" s="208"/>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-      <c r="N40" s="208"/>
+      <c r="C40" s="205"/>
+      <c r="D40" s="203"/>
+      <c r="E40" s="203"/>
+      <c r="F40" s="203"/>
+      <c r="G40" s="203"/>
+      <c r="H40" s="203"/>
+      <c r="I40" s="203"/>
+      <c r="J40" s="203"/>
+      <c r="K40" s="203"/>
+      <c r="L40" s="203"/>
+      <c r="M40" s="203"/>
+      <c r="N40" s="203"/>
       <c r="O40" s="94"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H41" s="79"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
       <c r="L41" s="95"/>
       <c r="N41" s="96"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L44" s="138"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L44" s="136"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L45" s="95"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E46" s="139"/>
-      <c r="F46" s="139"/>
-      <c r="G46" s="139"/>
-      <c r="H46" s="139"/>
-      <c r="I46" s="139"/>
-      <c r="J46" s="139"/>
-      <c r="K46" s="139"/>
-      <c r="L46" s="140"/>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E46" s="137"/>
+      <c r="F46" s="137"/>
+      <c r="G46" s="137"/>
+      <c r="H46" s="137"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="137"/>
+      <c r="K46" s="137"/>
+      <c r="L46" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5532,4 +5535,135 @@
   <pageSetup scale="85" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0BC2D6A-355E-4DA5-9817-628575299AB4}">
+  <dimension ref="D4:H25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" s="136">
+        <v>374177.79418060009</v>
+      </c>
+      <c r="G4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F5" s="136">
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F6" s="136">
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F8" s="136">
+        <f>SUM(F4:F7)</f>
+        <v>468461.09567764006</v>
+      </c>
+      <c r="G8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="136">
+        <v>-55000</v>
+      </c>
+      <c r="G10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F11" s="136">
+        <v>-384067</v>
+      </c>
+      <c r="G11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="4:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D13" s="207" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="207"/>
+      <c r="F13" s="189">
+        <f>SUM(F8:F12)</f>
+        <v>29394.095677640056</v>
+      </c>
+    </row>
+    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16" s="44">
+        <f>'prorrateo '!E19</f>
+        <v>294818.42106860003</v>
+      </c>
+      <c r="G16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="F17" s="136">
+        <v>36601.116018119996</v>
+      </c>
+      <c r="G17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="F18" s="136">
+        <v>36601.116018119996</v>
+      </c>
+      <c r="G18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="190">
+        <f>SUM(F13:F19)</f>
+        <v>397414.74878248002</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="22" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="F22" s="136"/>
+    </row>
+    <row r="23" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="F23" s="136"/>
+    </row>
+    <row r="25" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="F25" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/2026/ROSALES/Marzo/expensas rosales Marzo.xlsx
+++ b/2026/ROSALES/Marzo/expensas rosales Marzo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ROSALES\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ROSALES\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F9DCF9-DB78-451C-9021-04F1FB897679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0215EE7C-4430-4BA0-9DF1-A145AFC9AA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -25,6 +25,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'SITUACION ARIEL'!$D$4:$H$20</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1524,9 +1529,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1564,9 +1569,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1599,9 +1604,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1634,9 +1656,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1814,16 +1853,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1831,22 +1870,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
@@ -1857,51 +1896,51 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>102</v>
       </c>
@@ -1912,7 +1951,7 @@
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
@@ -1923,7 +1962,7 @@
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>25</v>
       </c>
@@ -1934,7 +1973,7 @@
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
         <v>120</v>
       </c>
@@ -1945,7 +1984,7 @@
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>131</v>
       </c>
@@ -1956,7 +1995,7 @@
       <c r="D22" s="20"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
         <v>11</v>
       </c>
@@ -1970,7 +2009,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="40"/>
       <c r="B24" s="41"/>
       <c r="C24" s="23">
@@ -1978,7 +2017,7 @@
         <v>1857766.54</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>12</v>
       </c>
@@ -1987,7 +2026,7 @@
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>96</v>
       </c>
@@ -1999,7 +2038,7 @@
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
         <v>97</v>
       </c>
@@ -2010,7 +2049,7 @@
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
         <v>114</v>
       </c>
@@ -2021,7 +2060,7 @@
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
         <v>121</v>
       </c>
@@ -2032,7 +2071,7 @@
       <c r="D29" s="45"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
         <v>106</v>
       </c>
@@ -2042,7 +2081,7 @@
       </c>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
         <v>91</v>
       </c>
@@ -2052,7 +2091,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="40"/>
       <c r="B32" s="41"/>
       <c r="C32" s="23">
@@ -2061,7 +2100,7 @@
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="30" t="s">
         <v>6</v>
       </c>
@@ -2072,40 +2111,40 @@
       </c>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C35" s="24"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
       <c r="C36" s="170"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
       <c r="C37" s="170"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="28"/>
       <c r="B38" s="28"/>
       <c r="C38" s="34"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C39" s="25"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="154" t="s">
         <v>113</v>
       </c>
@@ -2115,11 +2154,11 @@
       </c>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C41" s="25"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>15</v>
       </c>
@@ -2130,7 +2169,7 @@
       </c>
       <c r="E42" s="6"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
         <v>7</v>
       </c>
@@ -2140,13 +2179,13 @@
         <v>2370813.5499999998</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="C46" s="139"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="160" t="s">
         <v>98</v>
       </c>
@@ -2157,7 +2196,7 @@
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="160" t="s">
         <v>119</v>
       </c>
@@ -2169,7 +2208,7 @@
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="160" t="s">
         <v>95</v>
       </c>
@@ -2179,7 +2218,7 @@
         <v>3661916.314806771</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="160" t="s">
         <v>110</v>
       </c>
@@ -2188,7 +2227,7 @@
         <v>-1024355.45</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="160" t="s">
         <v>109</v>
       </c>
@@ -2197,7 +2236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="160" t="s">
         <v>8</v>
       </c>
@@ -2208,30 +2247,30 @@
       </c>
       <c r="D52" s="5"/>
     </row>
-    <row r="53" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9"/>
       <c r="B53" s="8"/>
       <c r="C53" s="10"/>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="195"/>
       <c r="B54" s="195"/>
       <c r="C54" s="195"/>
       <c r="F54" s="44"/>
     </row>
-    <row r="55" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="196"/>
       <c r="B55" s="196"/>
       <c r="C55" s="196"/>
     </row>
-    <row r="56" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B56" s="27"/>
       <c r="C56" s="29"/>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="28" t="s">
         <v>23</v>
       </c>
@@ -2241,17 +2280,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="28"/>
       <c r="B58" s="28"/>
       <c r="C58" s="31"/>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="28"/>
       <c r="B59" s="28"/>
       <c r="C59" s="32"/>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="140" t="s">
         <v>0</v>
       </c>
@@ -2261,24 +2300,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="197" t="s">
         <v>105</v>
       </c>
       <c r="B61" s="198"/>
       <c r="C61" s="198"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="198"/>
       <c r="B62" s="198"/>
       <c r="C62" s="198"/>
     </row>
-    <row r="63" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="198"/>
       <c r="B63" s="198"/>
       <c r="C63" s="198"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -2305,26 +2344,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="11" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
@@ -2360,7 +2399,7 @@
         <v>1034026.5</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2404,7 +2443,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2458,7 +2497,7 @@
         <v>121148.57240499997</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2507,7 +2546,7 @@
         <v>438130.07958308229</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2523,11 +2562,11 @@
       </c>
       <c r="F5" s="172">
         <f>240944.56-F23</f>
-        <v>240944.56</v>
+        <v>204343.44398188</v>
       </c>
       <c r="G5" s="178">
         <f t="shared" si="1"/>
-        <v>-36601.121249231277</v>
+        <v>-5.23111128131859E-3</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="2"/>
@@ -2551,15 +2590,15 @@
       </c>
       <c r="M5" s="57">
         <f t="shared" si="6"/>
-        <v>136717.38005748868</v>
+        <v>173318.49607560871</v>
       </c>
       <c r="N5" s="44"/>
       <c r="O5" s="136">
         <f t="shared" si="7"/>
-        <v>82887.881670768693</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>119488.99768888872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="62" t="s">
         <v>37</v>
       </c>
@@ -2611,7 +2650,7 @@
       </c>
       <c r="P6" s="156"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2665,7 +2704,7 @@
       </c>
       <c r="P7" s="156"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2716,7 +2755,7 @@
         <v>120674.40969499998</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2768,7 +2807,7 @@
       </c>
       <c r="P9" s="156"/>
     </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="185" t="s">
         <v>115</v>
       </c>
@@ -2816,7 +2855,7 @@
         <v>120674.21424886002</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>94</v>
       </c>
@@ -2867,7 +2906,7 @@
         <v>119489.00291999998</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2918,7 +2957,7 @@
         <v>123519.38595499999</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2972,7 +3011,7 @@
         <v>121148.67296384765</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
@@ -3022,7 +3061,7 @@
         <v>308657.49018362886</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3075,7 +3114,7 @@
         <v>158551.65656761589</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3129,7 +3168,7 @@
         <v>123459.07450228361</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3180,7 +3219,7 @@
         <v>119489.00292</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="164" t="s">
         <v>61</v>
       </c>
@@ -3234,7 +3273,7 @@
       <c r="P18" s="166"/>
       <c r="Q18" s="163"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
@@ -3285,7 +3324,7 @@
         <v>175440.20270000002</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="62" t="s">
         <v>116</v>
       </c>
@@ -3332,7 +3371,7 @@
         <v>461587.10425082408</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3383,7 +3422,7 @@
         <v>25604.786339999999</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="62" t="s">
         <v>115</v>
       </c>
@@ -3434,7 +3473,7 @@
         <v>25604.786339999999</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3448,14 +3487,17 @@
       <c r="E23" s="126">
         <v>36601.116018119996</v>
       </c>
-      <c r="F23" s="172"/>
+      <c r="F23" s="172">
+        <f>E23</f>
+        <v>36601.116018119996</v>
+      </c>
       <c r="G23" s="178">
         <f t="shared" si="1"/>
-        <v>36601.116018119996</v>
+        <v>0</v>
       </c>
       <c r="H23" s="56">
         <f t="shared" si="2"/>
-        <v>1464.0446407247998</v>
+        <v>0</v>
       </c>
       <c r="I23" s="56">
         <f t="shared" si="3"/>
@@ -3475,14 +3517,14 @@
       </c>
       <c r="M23" s="57">
         <f t="shared" si="6"/>
-        <v>73235.312510284799</v>
+        <v>35170.151851440001</v>
       </c>
       <c r="O23" s="136">
         <f t="shared" si="7"/>
-        <v>63669.946998844796</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+        <v>25604.786339999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3535,7 +3577,7 @@
         <v>25604.786339999999</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -3585,7 +3627,7 @@
         <v>63669.946998844796</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3636,7 +3678,7 @@
         <v>25604.786339999999</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3691,7 +3733,7 @@
         <v>368020.65310484002</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3743,7 +3785,7 @@
         <v>25604.786339999999</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3796,7 +3838,7 @@
         <v>25604.786339999999</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3811,7 +3853,7 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3840,16 +3882,16 @@
       <c r="L31" s="132"/>
       <c r="M31" s="132">
         <f>SUM(M3:M29)</f>
-        <v>4415121.5128804985</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>4413657.468239774</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K32" s="22"/>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F34" s="44"/>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E36" s="21"/>
     </row>
   </sheetData>
@@ -3868,26 +3910,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="5.21875" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="12.77734375" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="5.109375" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="5.140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="202" t="s">
         <v>77</v>
       </c>
@@ -3906,7 +3948,7 @@
       <c r="N1" s="204"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="143"/>
@@ -3924,7 +3966,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="145"/>
@@ -3942,7 +3984,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="145"/>
@@ -3962,7 +4004,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="145"/>
@@ -3980,7 +4022,7 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
       <c r="C6" s="169" t="str">
@@ -4001,7 +4043,7 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
@@ -4024,7 +4066,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -4049,7 +4091,7 @@
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="86" t="s">
         <v>78</v>
       </c>
@@ -4094,7 +4136,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="97">
         <v>1</v>
       </c>
@@ -4150,7 +4192,7 @@
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="98">
         <v>2</v>
       </c>
@@ -4206,7 +4248,7 @@
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="97">
         <v>3</v>
       </c>
@@ -4258,14 +4300,14 @@
       </c>
       <c r="O12" s="96">
         <f>N12+'prorrateo '!M5</f>
-        <v>190546.87844420868</v>
+        <v>227147.9944623287</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="97">
         <v>4</v>
       </c>
@@ -4321,7 +4363,7 @@
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="97">
         <v>6</v>
       </c>
@@ -4377,7 +4419,7 @@
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="97">
         <v>7</v>
       </c>
@@ -4432,7 +4474,7 @@
         <v>225880.27126023994</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="97">
         <v>8</v>
       </c>
@@ -4487,7 +4529,7 @@
         <v>227046.33996696002</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="97">
         <v>9</v>
       </c>
@@ -4542,7 +4584,7 @@
         <v>213800.31021410006</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="97">
         <v>10</v>
       </c>
@@ -4597,7 +4639,7 @@
         <v>220170.24689343991</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="97">
         <v>11</v>
       </c>
@@ -4652,7 +4694,7 @@
         <v>249401.95290056005</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="97">
         <v>12</v>
       </c>
@@ -4707,7 +4749,7 @@
         <v>241433.36632580764</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="97">
         <v>13</v>
       </c>
@@ -4762,7 +4804,7 @@
         <v>408911.39814886893</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="97">
         <v>14</v>
       </c>
@@ -4817,7 +4859,7 @@
         <v>270168.46474105585</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="97">
         <v>15</v>
       </c>
@@ -4872,7 +4914,7 @@
         <v>241801.16664784355</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="97">
         <v>16</v>
       </c>
@@ -4927,7 +4969,7 @@
         <v>212892.37569343997</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="97">
         <v>17</v>
       </c>
@@ -4982,7 +5024,7 @@
         <v>228187.33350055999</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="97">
         <v>18</v>
       </c>
@@ -5037,7 +5079,7 @@
         <v>329911.61528640019</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="187">
         <v>19</v>
       </c>
@@ -5079,7 +5121,7 @@
         <v>480717.83527370403</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="97">
         <v>20</v>
       </c>
@@ -5118,7 +5160,7 @@
         <v>44735.517362880004</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="97"/>
       <c r="B29" s="89"/>
       <c r="C29" s="150" t="s">
@@ -5150,7 +5192,7 @@
         <v>44735.517362880004</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="97"/>
       <c r="B30" s="89"/>
       <c r="C30" s="150" t="s">
@@ -5179,10 +5221,10 @@
       </c>
       <c r="O30" s="96">
         <f>N30+'prorrateo '!M23</f>
-        <v>82800.678021724802</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>44735.517362880004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="97"/>
       <c r="B31" s="89"/>
       <c r="C31" s="150" t="s">
@@ -5216,7 +5258,7 @@
         <v>44735.517362880004</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="98"/>
       <c r="B32" s="168"/>
       <c r="C32" s="150" t="s">
@@ -5250,7 +5292,7 @@
         <v>82800.678021724802</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="97"/>
       <c r="B33" s="89"/>
       <c r="C33" s="127" t="s">
@@ -5284,7 +5326,7 @@
         <v>44735.517362880004</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="97"/>
       <c r="B34" s="89"/>
       <c r="C34" s="127" t="s">
@@ -5318,7 +5360,7 @@
         <v>44735.517362880004</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="97">
         <v>21</v>
       </c>
@@ -5357,7 +5399,7 @@
         <v>44735.517362880004</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="97">
         <v>22</v>
       </c>
@@ -5398,7 +5440,7 @@
         <v>44735.517362880004</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="97">
         <v>23</v>
       </c>
@@ -5428,7 +5470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="97">
         <v>24</v>
       </c>
@@ -5456,7 +5498,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
       <c r="C39" s="90"/>
       <c r="D39" s="91"/>
@@ -5481,7 +5523,7 @@
       <c r="N39" s="92"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="94" t="s">
         <v>88</v>
       </c>
@@ -5499,23 +5541,23 @@
       <c r="N40" s="203"/>
       <c r="O40" s="94"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="79"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
       <c r="L41" s="95"/>
       <c r="N41" s="96"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="136"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="95"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="137"/>
       <c r="F46" s="137"/>
       <c r="G46" s="137"/>
@@ -5540,12 +5582,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0BC2D6A-355E-4DA5-9817-628575299AB4}">
   <dimension ref="D4:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>122</v>
       </c>
@@ -5556,7 +5598,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F5" s="136">
         <v>47141.650748520005</v>
       </c>
@@ -5564,7 +5606,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F6" s="136">
         <v>47141.650748520005</v>
       </c>
@@ -5572,7 +5614,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F8" s="136">
         <f>SUM(F4:F7)</f>
         <v>468461.09567764006</v>
@@ -5581,7 +5623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>126</v>
       </c>
@@ -5592,7 +5634,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F11" s="136">
         <v>-384067</v>
       </c>
@@ -5600,7 +5642,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="4:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="4:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="207" t="s">
         <v>128</v>
       </c>
@@ -5610,7 +5652,7 @@
         <v>29394.095677640056</v>
       </c>
     </row>
-    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>129</v>
       </c>
@@ -5622,7 +5664,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="17" spans="4:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:8" x14ac:dyDescent="0.25">
       <c r="F17" s="136">
         <v>36601.116018119996</v>
       </c>
@@ -5630,7 +5672,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="4:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:8" x14ac:dyDescent="0.25">
       <c r="F18" s="136">
         <v>36601.116018119996</v>
       </c>
@@ -5638,7 +5680,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="4:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="190">
@@ -5650,13 +5692,13 @@
       </c>
       <c r="H20" s="4"/>
     </row>
-    <row r="22" spans="4:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:8" x14ac:dyDescent="0.25">
       <c r="F22" s="136"/>
     </row>
-    <row r="23" spans="4:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:8" x14ac:dyDescent="0.25">
       <c r="F23" s="136"/>
     </row>
-    <row r="25" spans="4:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:8" x14ac:dyDescent="0.25">
       <c r="F25" s="44"/>
     </row>
   </sheetData>
